--- a/data/stx_xlsx/MOMENT.ST.xlsx
+++ b/data/stx_xlsx/MOMENT.ST.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="327">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -556,6 +556,9 @@
   </si>
   <si>
     <t>Total current liabilities</t>
+  </si>
+  <si>
+    <t>Interest-bearing liabilities (Do not use)</t>
   </si>
   <si>
     <t>Lease liabilities</t>
@@ -1122,7 +1125,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1211,6 +1214,9 @@
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -6449,8 +6455,8 @@
       </c>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="14" t="s">
-        <v>168</v>
+      <c r="A71" s="30" t="s">
+        <v>179</v>
       </c>
       <c r="B71" s="15">
         <v>120.28</v>
@@ -6475,7 +6481,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B72" s="15">
         <v>416.61</v>
@@ -6502,7 +6508,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B73" s="17">
         <v>12.03</v>
@@ -6527,7 +6533,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B74" s="16"/>
       <c r="C74" s="17">
@@ -6550,7 +6556,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B75" s="16"/>
       <c r="C75" s="16">
@@ -6577,7 +6583,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B76" s="16"/>
       <c r="C76" s="16"/>
@@ -6592,7 +6598,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B77" s="16"/>
       <c r="C77" s="16"/>
@@ -6607,7 +6613,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="21" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B78" s="19">
         <v>548.92</v>
@@ -6636,7 +6642,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B79" s="19">
         <v>976.47</v>
@@ -6665,7 +6671,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B80" s="17">
         <v>68.89</v>
@@ -6694,7 +6700,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B81" s="15">
         <v>164.02</v>
@@ -6723,7 +6729,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B82" s="20">
         <v>-1.09</v>
@@ -6752,7 +6758,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B83" s="27">
         <v>-132.31</v>
@@ -6781,7 +6787,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="21" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B84" s="23">
         <v>99.51</v>
@@ -6810,7 +6816,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B85" s="17">
         <v>1.09</v>
@@ -6839,7 +6845,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="21" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B86" s="19">
         <v>100.6</v>
@@ -6868,7 +6874,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B87" s="19">
         <v>1077.06</v>
@@ -6897,7 +6903,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B88" s="17">
         <v>25.32</v>
@@ -6926,7 +6932,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B89" s="17">
         <v>25.32</v>
@@ -6955,7 +6961,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B90" s="17">
         <v>1.0</v>
@@ -6984,7 +6990,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B91" s="17">
         <v>25.32</v>
@@ -7013,7 +7019,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B92" s="17">
         <v>25.32</v>
@@ -7970,7 +7976,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8174,28 +8180,28 @@
         <v>30</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -8229,7 +8235,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -8271,7 +8277,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B20" s="17">
         <v>46.6</v>
@@ -8329,7 +8335,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B22" s="17">
         <v>7.41</v>
@@ -8358,7 +8364,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B23" s="16"/>
       <c r="C23" s="16"/>
@@ -8375,7 +8381,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -8394,7 +8400,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B25" s="20">
         <v>-4.24</v>
@@ -8423,7 +8429,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B26" s="17">
         <v>2.12</v>
@@ -8452,7 +8458,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B27" s="20">
         <v>-39.19</v>
@@ -8481,7 +8487,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -8496,7 +8502,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B29" s="16"/>
       <c r="C29" s="17">
@@ -8523,7 +8529,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B30" s="17">
         <v>11.65</v>
@@ -8552,7 +8558,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B31" s="17">
         <v>32.83</v>
@@ -8581,7 +8587,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
@@ -8596,7 +8602,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B33" s="20">
         <v>-1.06</v>
@@ -8617,7 +8623,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="21" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B34" s="23">
         <v>91.09</v>
@@ -8646,7 +8652,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
@@ -8663,7 +8669,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B36" s="16">
         <v>0.0</v>
@@ -8686,7 +8692,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B37" s="20">
         <v>-2.12</v>
@@ -8711,7 +8717,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
@@ -8728,7 +8734,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B39" s="20">
         <v>-23.3</v>
@@ -8749,7 +8755,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B40" s="16"/>
       <c r="C40" s="16"/>
@@ -8770,7 +8776,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B41" s="16"/>
       <c r="C41" s="20">
@@ -8787,7 +8793,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B42" s="17">
         <v>2.12</v>
@@ -8806,7 +8812,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B43" s="16"/>
       <c r="C43" s="16"/>
@@ -8827,7 +8833,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B44" s="20">
         <v>-1.06</v>
@@ -8842,7 +8848,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B45" s="17">
         <v>66.73</v>
@@ -8857,7 +8863,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="21" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B46" s="23">
         <v>42.37</v>
@@ -8886,7 +8892,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B47" s="16">
         <v>0.0</v>
@@ -8911,7 +8917,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B48" s="16">
         <v>0.0</v>
@@ -8928,7 +8934,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B49" s="16"/>
       <c r="C49" s="16"/>
@@ -8945,7 +8951,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B50" s="20">
         <v>-25.42</v>
@@ -8966,7 +8972,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B51" s="20">
         <v>-40.25</v>
@@ -8991,7 +8997,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B52" s="16"/>
       <c r="C52" s="16"/>
@@ -9014,7 +9020,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B53" s="16"/>
       <c r="C53" s="16"/>
@@ -9033,7 +9039,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B54" s="16">
         <v>0.0</v>
@@ -9056,7 +9062,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B55" s="16"/>
       <c r="C55" s="16"/>
@@ -9073,7 +9079,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
@@ -9094,7 +9100,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B57" s="17">
         <v>1.06</v>
@@ -9109,7 +9115,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="21" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B58" s="24">
         <v>-64.61</v>
@@ -9138,7 +9144,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B59" s="20">
         <v>-2.12</v>
@@ -9167,7 +9173,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B60" s="15">
         <v>121.37</v>
@@ -9196,7 +9202,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B61" s="15">
         <v>189.17</v>
@@ -9225,7 +9231,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B62" s="17">
         <v>67.79</v>
@@ -9254,7 +9260,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B63" s="23">
         <v>66.73</v>
@@ -10240,7 +10246,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -10362,46 +10368,46 @@
         <v>25</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="R11" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="S11" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="T11" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="U11" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="V11" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -10746,7 +10752,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -10796,2599 +10802,2599 @@
         <v>42</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M19" s="13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O19" s="13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P19" s="13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q19" s="13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R19" s="13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="S19" s="13" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="T19" s="13" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="U19" s="13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="V19" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="31"/>
-      <c r="N20" s="31"/>
-      <c r="O20" s="31"/>
-      <c r="P20" s="31"/>
-      <c r="Q20" s="31"/>
-      <c r="R20" s="31"/>
-      <c r="S20" s="31"/>
-      <c r="T20" s="31"/>
-      <c r="U20" s="31"/>
-      <c r="V20" s="31"/>
+      <c r="A20" s="31" t="s">
+        <v>276</v>
+      </c>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="32"/>
+      <c r="R20" s="32"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="32"/>
+      <c r="V20" s="32"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="32" t="s">
-        <v>275</v>
-      </c>
-      <c r="B21" s="33">
+      <c r="A21" s="33" t="s">
+        <v>276</v>
+      </c>
+      <c r="B21" s="34">
         <v>723.14</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="34">
         <v>764.65</v>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="34">
         <v>556.54</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="34">
         <v>688.87</v>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="34">
         <v>679.82</v>
       </c>
-      <c r="G21" s="33">
+      <c r="G21" s="34">
         <v>633.76</v>
       </c>
-      <c r="H21" s="33">
+      <c r="H21" s="34">
         <v>840.96</v>
       </c>
-      <c r="I21" s="33">
+      <c r="I21" s="34">
         <v>208.84</v>
       </c>
-      <c r="J21" s="33">
+      <c r="J21" s="34">
         <v>424.59</v>
       </c>
-      <c r="K21" s="33">
+      <c r="K21" s="34">
         <v>196.75</v>
       </c>
-      <c r="L21" s="34">
+      <c r="L21" s="35">
         <v>64.51</v>
       </c>
-      <c r="M21" s="33">
+      <c r="M21" s="34">
         <v>132.89</v>
       </c>
-      <c r="N21" s="34">
+      <c r="N21" s="35">
         <v>88.2</v>
       </c>
-      <c r="O21" s="33">
+      <c r="O21" s="34">
         <v>118.98</v>
       </c>
-      <c r="P21" s="33">
+      <c r="P21" s="34">
         <v>119.97</v>
       </c>
-      <c r="Q21" s="33">
+      <c r="Q21" s="34">
         <v>106.7</v>
       </c>
-      <c r="R21" s="34">
+      <c r="R21" s="35">
         <v>43.49</v>
       </c>
-      <c r="S21" s="33">
+      <c r="S21" s="34">
         <v>163.46</v>
       </c>
-      <c r="T21" s="33">
+      <c r="T21" s="34">
         <v>209.71</v>
       </c>
-      <c r="U21" s="34">
+      <c r="U21" s="35">
         <v>92.36</v>
       </c>
-      <c r="V21" s="34">
+      <c r="V21" s="35">
         <v>27.87</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="32" t="s">
-        <v>276</v>
-      </c>
-      <c r="B22" s="33">
+      <c r="A22" s="33" t="s">
+        <v>277</v>
+      </c>
+      <c r="B22" s="34">
         <v>701.63</v>
       </c>
-      <c r="C22" s="33">
+      <c r="C22" s="34">
         <v>681.53</v>
       </c>
-      <c r="D22" s="33">
+      <c r="D22" s="34">
         <v>656.44</v>
       </c>
-      <c r="E22" s="33">
+      <c r="E22" s="34">
         <v>604.92</v>
       </c>
-      <c r="F22" s="33">
+      <c r="F22" s="34">
         <v>594.18</v>
       </c>
-      <c r="G22" s="33">
+      <c r="G22" s="34">
         <v>446.72</v>
       </c>
-      <c r="H22" s="33">
+      <c r="H22" s="34">
         <v>346.14</v>
       </c>
-      <c r="I22" s="33">
+      <c r="I22" s="34">
         <v>210.68</v>
       </c>
-      <c r="J22" s="33">
+      <c r="J22" s="34">
         <v>179.62</v>
       </c>
-      <c r="K22" s="33">
+      <c r="K22" s="34">
         <v>133.22</v>
       </c>
-      <c r="L22" s="33">
+      <c r="L22" s="34">
         <v>112.48</v>
       </c>
-      <c r="M22" s="33">
+      <c r="M22" s="34">
         <v>122.76</v>
       </c>
-      <c r="N22" s="34">
+      <c r="N22" s="35">
         <v>95.74</v>
       </c>
-      <c r="O22" s="33">
+      <c r="O22" s="34">
         <v>112.89</v>
       </c>
-      <c r="P22" s="33">
+      <c r="P22" s="34">
         <v>129.06</v>
       </c>
-      <c r="Q22" s="33">
+      <c r="Q22" s="34">
         <v>115.58</v>
       </c>
-      <c r="R22" s="33">
+      <c r="R22" s="34">
         <v>109.0</v>
       </c>
-      <c r="S22" s="35"/>
-      <c r="T22" s="35"/>
-      <c r="U22" s="35"/>
-      <c r="V22" s="35"/>
+      <c r="S22" s="36"/>
+      <c r="T22" s="36"/>
+      <c r="U22" s="36"/>
+      <c r="V22" s="36"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="30" t="s">
-        <v>277</v>
-      </c>
-      <c r="B23" s="31"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="31"/>
-      <c r="L23" s="31"/>
-      <c r="M23" s="31"/>
-      <c r="N23" s="31"/>
-      <c r="O23" s="31"/>
-      <c r="P23" s="31"/>
-      <c r="Q23" s="31"/>
-      <c r="R23" s="31"/>
-      <c r="S23" s="31"/>
-      <c r="T23" s="31"/>
-      <c r="U23" s="31"/>
-      <c r="V23" s="31"/>
+      <c r="A23" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
+      <c r="N23" s="32"/>
+      <c r="O23" s="32"/>
+      <c r="P23" s="32"/>
+      <c r="Q23" s="32"/>
+      <c r="R23" s="32"/>
+      <c r="S23" s="32"/>
+      <c r="T23" s="32"/>
+      <c r="U23" s="32"/>
+      <c r="V23" s="32"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="B24" s="33">
+      <c r="A24" s="33" t="s">
+        <v>278</v>
+      </c>
+      <c r="B24" s="34">
         <v>229.04</v>
       </c>
-      <c r="C24" s="33">
+      <c r="C24" s="34">
         <v>313.98</v>
       </c>
-      <c r="D24" s="33">
+      <c r="D24" s="34">
         <v>236.34</v>
       </c>
-      <c r="E24" s="33">
+      <c r="E24" s="34">
         <v>313.69</v>
       </c>
-      <c r="F24" s="34">
+      <c r="F24" s="35">
         <v>55.83</v>
       </c>
-      <c r="G24" s="33">
+      <c r="G24" s="34">
         <v>127.1</v>
       </c>
-      <c r="H24" s="33">
+      <c r="H24" s="34">
         <v>284.72</v>
       </c>
-      <c r="I24" s="33">
+      <c r="I24" s="34">
         <v>237.05</v>
       </c>
-      <c r="J24" s="33">
+      <c r="J24" s="34">
         <v>249.62</v>
       </c>
-      <c r="K24" s="33">
+      <c r="K24" s="34">
         <v>342.97</v>
       </c>
-      <c r="L24" s="33">
+      <c r="L24" s="34">
         <v>157.06</v>
       </c>
-      <c r="M24" s="33">
+      <c r="M24" s="34">
         <v>151.33</v>
       </c>
-      <c r="N24" s="33">
+      <c r="N24" s="34">
         <v>127.31</v>
       </c>
-      <c r="O24" s="33">
+      <c r="O24" s="34">
         <v>130.76</v>
       </c>
-      <c r="P24" s="33">
+      <c r="P24" s="34">
         <v>189.56</v>
       </c>
-      <c r="Q24" s="33">
+      <c r="Q24" s="34">
         <v>188.54</v>
       </c>
-      <c r="R24" s="34">
+      <c r="R24" s="35">
         <v>85.85</v>
       </c>
-      <c r="S24" s="33">
+      <c r="S24" s="34">
         <v>183.79</v>
       </c>
-      <c r="T24" s="33">
+      <c r="T24" s="34">
         <v>270.11</v>
       </c>
-      <c r="U24" s="33">
+      <c r="U24" s="34">
         <v>133.94</v>
       </c>
-      <c r="V24" s="34">
+      <c r="V24" s="35">
         <v>44.02</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="32" t="s">
-        <v>278</v>
-      </c>
-      <c r="B25" s="33">
+      <c r="A25" s="33" t="s">
+        <v>279</v>
+      </c>
+      <c r="B25" s="34">
         <v>238.76</v>
       </c>
-      <c r="C25" s="33">
+      <c r="C25" s="34">
         <v>216.24</v>
       </c>
-      <c r="D25" s="33">
+      <c r="D25" s="34">
         <v>198.39</v>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="34">
         <v>202.58</v>
       </c>
-      <c r="F25" s="33">
+      <c r="F25" s="34">
         <v>204.85</v>
       </c>
-      <c r="G25" s="33">
+      <c r="G25" s="34">
         <v>235.38</v>
       </c>
-      <c r="H25" s="33">
+      <c r="H25" s="34">
         <v>250.49</v>
       </c>
-      <c r="I25" s="33">
+      <c r="I25" s="34">
         <v>230.6</v>
       </c>
-      <c r="J25" s="33">
+      <c r="J25" s="34">
         <v>201.82</v>
       </c>
-      <c r="K25" s="33">
+      <c r="K25" s="34">
         <v>199.17</v>
       </c>
-      <c r="L25" s="33">
+      <c r="L25" s="34">
         <v>161.47</v>
       </c>
-      <c r="M25" s="33">
+      <c r="M25" s="34">
         <v>171.8</v>
       </c>
-      <c r="N25" s="33">
+      <c r="N25" s="34">
         <v>145.09</v>
       </c>
-      <c r="O25" s="33">
+      <c r="O25" s="34">
         <v>159.18</v>
       </c>
-      <c r="P25" s="33">
+      <c r="P25" s="34">
         <v>184.5</v>
       </c>
-      <c r="Q25" s="33">
+      <c r="Q25" s="34">
         <v>162.23</v>
       </c>
-      <c r="R25" s="33">
+      <c r="R25" s="34">
         <v>145.42</v>
       </c>
-      <c r="S25" s="35"/>
-      <c r="T25" s="35"/>
-      <c r="U25" s="35"/>
-      <c r="V25" s="35"/>
+      <c r="S25" s="36"/>
+      <c r="T25" s="36"/>
+      <c r="U25" s="36"/>
+      <c r="V25" s="36"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="31"/>
-      <c r="N26" s="31"/>
-      <c r="O26" s="31"/>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
-      <c r="S26" s="31"/>
-      <c r="T26" s="31"/>
-      <c r="U26" s="31"/>
-      <c r="V26" s="31"/>
+      <c r="A26" s="31" t="s">
+        <v>280</v>
+      </c>
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="32"/>
+      <c r="O26" s="32"/>
+      <c r="P26" s="32"/>
+      <c r="Q26" s="32"/>
+      <c r="R26" s="32"/>
+      <c r="S26" s="32"/>
+      <c r="T26" s="32"/>
+      <c r="U26" s="32"/>
+      <c r="V26" s="32"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="32" t="s">
-        <v>280</v>
-      </c>
-      <c r="B27" s="34">
+      <c r="A27" s="33" t="s">
+        <v>281</v>
+      </c>
+      <c r="B27" s="35">
         <v>9.05</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="35">
         <v>12.6</v>
       </c>
-      <c r="D27" s="34">
+      <c r="D27" s="35">
         <v>10.46</v>
       </c>
-      <c r="E27" s="34">
+      <c r="E27" s="35">
         <v>13.89</v>
       </c>
-      <c r="F27" s="34">
+      <c r="F27" s="35">
         <v>6.08</v>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="35">
         <v>13.84</v>
       </c>
-      <c r="H27" s="34">
+      <c r="H27" s="35">
         <v>42.56</v>
       </c>
-      <c r="I27" s="34">
+      <c r="I27" s="35">
         <v>40.39</v>
       </c>
-      <c r="J27" s="34">
+      <c r="J27" s="35">
         <v>42.53</v>
       </c>
-      <c r="K27" s="34">
+      <c r="K27" s="35">
         <v>58.43</v>
       </c>
-      <c r="L27" s="34">
+      <c r="L27" s="35">
         <v>26.76</v>
       </c>
-      <c r="M27" s="34">
+      <c r="M27" s="35">
         <v>25.78</v>
       </c>
-      <c r="N27" s="34">
+      <c r="N27" s="35">
         <v>21.69</v>
       </c>
-      <c r="O27" s="34">
+      <c r="O27" s="35">
         <v>22.28</v>
       </c>
-      <c r="P27" s="34">
+      <c r="P27" s="35">
         <v>32.29</v>
       </c>
-      <c r="Q27" s="34">
+      <c r="Q27" s="35">
         <v>32.11</v>
       </c>
-      <c r="R27" s="34">
+      <c r="R27" s="35">
         <v>18.97</v>
       </c>
-      <c r="S27" s="34">
+      <c r="S27" s="35">
         <v>40.61</v>
       </c>
-      <c r="T27" s="34">
+      <c r="T27" s="35">
         <v>59.68</v>
       </c>
-      <c r="U27" s="34">
+      <c r="U27" s="35">
         <v>29.64</v>
       </c>
-      <c r="V27" s="34">
+      <c r="V27" s="35">
         <v>9.74</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="32" t="s">
-        <v>281</v>
-      </c>
-      <c r="B28" s="34">
+      <c r="A28" s="33" t="s">
+        <v>282</v>
+      </c>
+      <c r="B28" s="35">
         <v>10.8</v>
       </c>
-      <c r="C28" s="34">
+      <c r="C28" s="35">
         <v>11.77</v>
       </c>
-      <c r="D28" s="34">
+      <c r="D28" s="35">
         <v>16.86</v>
       </c>
-      <c r="E28" s="34">
+      <c r="E28" s="35">
         <v>23.15</v>
       </c>
-      <c r="F28" s="34">
+      <c r="F28" s="35">
         <v>31.2</v>
       </c>
-      <c r="G28" s="34">
+      <c r="G28" s="35">
         <v>37.4</v>
       </c>
-      <c r="H28" s="34">
+      <c r="H28" s="35">
         <v>41.49</v>
       </c>
-      <c r="I28" s="34">
+      <c r="I28" s="35">
         <v>39.29</v>
       </c>
-      <c r="J28" s="34">
+      <c r="J28" s="35">
         <v>34.38</v>
       </c>
-      <c r="K28" s="34">
+      <c r="K28" s="35">
         <v>33.93</v>
       </c>
-      <c r="L28" s="34">
+      <c r="L28" s="35">
         <v>27.51</v>
       </c>
-      <c r="M28" s="34">
+      <c r="M28" s="35">
         <v>29.27</v>
       </c>
-      <c r="N28" s="34">
+      <c r="N28" s="35">
         <v>25.55</v>
       </c>
-      <c r="O28" s="34">
+      <c r="O28" s="35">
         <v>29.88</v>
       </c>
-      <c r="P28" s="34">
+      <c r="P28" s="35">
         <v>36.8</v>
       </c>
-      <c r="Q28" s="34">
+      <c r="Q28" s="35">
         <v>33.94</v>
       </c>
-      <c r="R28" s="34">
+      <c r="R28" s="35">
         <v>32.14</v>
       </c>
-      <c r="S28" s="35"/>
-      <c r="T28" s="35"/>
-      <c r="U28" s="35"/>
-      <c r="V28" s="35"/>
+      <c r="S28" s="36"/>
+      <c r="T28" s="36"/>
+      <c r="U28" s="36"/>
+      <c r="V28" s="36"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="30" t="s">
-        <v>282</v>
-      </c>
-      <c r="B29" s="31"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="31"/>
-      <c r="N29" s="31"/>
-      <c r="O29" s="31"/>
-      <c r="P29" s="31"/>
-      <c r="Q29" s="31"/>
-      <c r="R29" s="31"/>
-      <c r="S29" s="31"/>
-      <c r="T29" s="31"/>
-      <c r="U29" s="31"/>
-      <c r="V29" s="31"/>
+      <c r="A29" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="B29" s="32"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="32"/>
+      <c r="M29" s="32"/>
+      <c r="N29" s="32"/>
+      <c r="O29" s="32"/>
+      <c r="P29" s="32"/>
+      <c r="Q29" s="32"/>
+      <c r="R29" s="32"/>
+      <c r="S29" s="32"/>
+      <c r="T29" s="32"/>
+      <c r="U29" s="32"/>
+      <c r="V29" s="32"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="32" t="s">
-        <v>283</v>
-      </c>
-      <c r="B30" s="36">
+      <c r="A30" s="33" t="s">
+        <v>284</v>
+      </c>
+      <c r="B30" s="37">
         <v>28.15</v>
       </c>
-      <c r="C30" s="36">
+      <c r="C30" s="37">
         <v>5.25</v>
       </c>
-      <c r="D30" s="36">
+      <c r="D30" s="37">
         <v>30.33</v>
       </c>
-      <c r="E30" s="36">
+      <c r="E30" s="37">
         <v>27.79</v>
       </c>
-      <c r="F30" s="37">
+      <c r="F30" s="38">
         <v>-113.57</v>
       </c>
-      <c r="G30" s="36">
+      <c r="G30" s="37">
         <v>50.95</v>
       </c>
-      <c r="H30" s="37">
+      <c r="H30" s="38">
         <v>-67.68</v>
       </c>
-      <c r="I30" s="37">
+      <c r="I30" s="38">
         <v>-7.19</v>
       </c>
-      <c r="J30" s="37">
+      <c r="J30" s="38">
         <v>-10.98</v>
       </c>
-      <c r="K30" s="36">
+      <c r="K30" s="37">
         <v>21.73</v>
       </c>
-      <c r="L30" s="36">
+      <c r="L30" s="37">
         <v>8.27</v>
       </c>
-      <c r="M30" s="37">
+      <c r="M30" s="38">
         <v>-3.73</v>
       </c>
-      <c r="N30" s="36">
+      <c r="N30" s="37">
         <v>25.5</v>
       </c>
-      <c r="O30" s="37">
+      <c r="O30" s="38">
         <v>-40.86</v>
       </c>
-      <c r="P30" s="36">
+      <c r="P30" s="37">
         <v>5.62</v>
       </c>
-      <c r="Q30" s="36">
+      <c r="Q30" s="37">
         <v>33.47</v>
       </c>
-      <c r="R30" s="36">
+      <c r="R30" s="37">
         <v>32.72</v>
       </c>
-      <c r="S30" s="36">
+      <c r="S30" s="37">
         <v>5.81</v>
       </c>
-      <c r="T30" s="36">
+      <c r="T30" s="37">
         <v>7.22</v>
       </c>
-      <c r="U30" s="36">
+      <c r="U30" s="37">
         <v>19.23</v>
       </c>
-      <c r="V30" s="36">
+      <c r="V30" s="37">
         <v>18.43</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="32" t="s">
-        <v>284</v>
-      </c>
-      <c r="B31" s="36">
+      <c r="A31" s="33" t="s">
+        <v>285</v>
+      </c>
+      <c r="B31" s="37">
         <v>7.34</v>
       </c>
-      <c r="C31" s="36">
+      <c r="C31" s="37">
         <v>15.22</v>
       </c>
-      <c r="D31" s="37">
+      <c r="D31" s="38">
         <v>-23.75</v>
       </c>
-      <c r="E31" s="37">
+      <c r="E31" s="38">
         <v>-23.19</v>
       </c>
-      <c r="F31" s="37">
+      <c r="F31" s="38">
         <v>-24.39</v>
       </c>
-      <c r="G31" s="37">
+      <c r="G31" s="38">
         <v>-8.87</v>
       </c>
-      <c r="H31" s="37">
+      <c r="H31" s="38">
         <v>-10.77</v>
       </c>
-      <c r="I31" s="36">
+      <c r="I31" s="37">
         <v>2.85</v>
       </c>
-      <c r="J31" s="36">
+      <c r="J31" s="37">
         <v>8.25</v>
       </c>
-      <c r="K31" s="36">
+      <c r="K31" s="37">
         <v>5.79</v>
       </c>
-      <c r="L31" s="37">
+      <c r="L31" s="38">
         <v>-0.45</v>
       </c>
-      <c r="M31" s="36">
+      <c r="M31" s="37">
         <v>6.65</v>
       </c>
-      <c r="N31" s="36">
+      <c r="N31" s="37">
         <v>12.28</v>
       </c>
-      <c r="O31" s="36">
+      <c r="O31" s="37">
         <v>8.52</v>
       </c>
-      <c r="P31" s="36">
+      <c r="P31" s="37">
         <v>14.1</v>
       </c>
-      <c r="Q31" s="36">
+      <c r="Q31" s="37">
         <v>16.46</v>
       </c>
-      <c r="R31" s="36">
+      <c r="R31" s="37">
         <v>12.84</v>
       </c>
-      <c r="S31" s="36"/>
-      <c r="T31" s="36"/>
-      <c r="U31" s="36"/>
-      <c r="V31" s="36"/>
+      <c r="S31" s="37"/>
+      <c r="T31" s="37"/>
+      <c r="U31" s="37"/>
+      <c r="V31" s="37"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="30" t="s">
-        <v>285</v>
-      </c>
-      <c r="B32" s="31"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="31"/>
-      <c r="L32" s="31"/>
-      <c r="M32" s="31"/>
-      <c r="N32" s="31"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="31"/>
-      <c r="Q32" s="31"/>
-      <c r="R32" s="31"/>
-      <c r="S32" s="31"/>
-      <c r="T32" s="31"/>
-      <c r="U32" s="31"/>
-      <c r="V32" s="31"/>
+      <c r="A32" s="31" t="s">
+        <v>286</v>
+      </c>
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
+      <c r="O32" s="32"/>
+      <c r="P32" s="32"/>
+      <c r="Q32" s="32"/>
+      <c r="R32" s="32"/>
+      <c r="S32" s="32"/>
+      <c r="T32" s="32"/>
+      <c r="U32" s="32"/>
+      <c r="V32" s="32"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="32" t="s">
-        <v>286</v>
-      </c>
-      <c r="B33" s="36">
+      <c r="A33" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="B33" s="37">
         <v>0.0</v>
       </c>
-      <c r="C33" s="36">
+      <c r="C33" s="37">
         <v>0.0</v>
       </c>
-      <c r="D33" s="36">
+      <c r="D33" s="37">
         <v>0.0</v>
       </c>
-      <c r="E33" s="36">
+      <c r="E33" s="37">
         <v>0.0</v>
       </c>
-      <c r="F33" s="36">
+      <c r="F33" s="37">
         <v>0.0</v>
       </c>
-      <c r="G33" s="36">
+      <c r="G33" s="37">
         <v>0.0</v>
       </c>
-      <c r="H33" s="36">
+      <c r="H33" s="37">
         <v>1.66</v>
       </c>
-      <c r="I33" s="36">
+      <c r="I33" s="37">
         <v>0.0</v>
       </c>
-      <c r="J33" s="36">
+      <c r="J33" s="37">
         <v>5.25</v>
       </c>
-      <c r="K33" s="36">
+      <c r="K33" s="37">
         <v>6.18</v>
       </c>
-      <c r="L33" s="36">
+      <c r="L33" s="37">
         <v>11.24</v>
       </c>
-      <c r="M33" s="36">
+      <c r="M33" s="37">
         <v>3.44</v>
       </c>
-      <c r="N33" s="36">
+      <c r="N33" s="37">
         <v>1.49</v>
       </c>
-      <c r="O33" s="36">
+      <c r="O33" s="37">
         <v>2.32</v>
       </c>
-      <c r="P33" s="36">
+      <c r="P33" s="37">
         <v>2.32</v>
       </c>
-      <c r="Q33" s="36">
+      <c r="Q33" s="37">
         <v>2.39</v>
       </c>
-      <c r="R33" s="36">
+      <c r="R33" s="37">
         <v>7.0</v>
       </c>
-      <c r="S33" s="36">
+      <c r="S33" s="37">
         <v>4.22</v>
       </c>
-      <c r="T33" s="36">
+      <c r="T33" s="37">
         <v>1.04</v>
       </c>
-      <c r="U33" s="36">
+      <c r="U33" s="37">
         <v>0.0</v>
       </c>
-      <c r="V33" s="36">
+      <c r="V33" s="37">
         <v>0.0</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="32" t="s">
-        <v>287</v>
-      </c>
-      <c r="B34" s="36">
+      <c r="A34" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="B34" s="37">
         <v>0.0</v>
       </c>
-      <c r="C34" s="36">
+      <c r="C34" s="37">
         <v>0.0</v>
       </c>
-      <c r="D34" s="36">
+      <c r="D34" s="37">
         <v>0.81</v>
       </c>
-      <c r="E34" s="36">
+      <c r="E34" s="37">
         <v>0.61</v>
       </c>
-      <c r="F34" s="36">
+      <c r="F34" s="37">
         <v>2.06</v>
       </c>
-      <c r="G34" s="36">
+      <c r="G34" s="37">
         <v>3.27</v>
       </c>
-      <c r="H34" s="36">
+      <c r="H34" s="37">
         <v>4.55</v>
       </c>
-      <c r="I34" s="36">
+      <c r="I34" s="37">
         <v>5.04</v>
       </c>
-      <c r="J34" s="36">
+      <c r="J34" s="37">
         <v>5.66</v>
       </c>
-      <c r="K34" s="36">
+      <c r="K34" s="37">
         <v>5.25</v>
       </c>
-      <c r="L34" s="36">
+      <c r="L34" s="37">
         <v>4.12</v>
       </c>
-      <c r="M34" s="36">
+      <c r="M34" s="37">
         <v>2.4</v>
       </c>
-      <c r="N34" s="36">
+      <c r="N34" s="37">
         <v>2.87</v>
       </c>
-      <c r="O34" s="36">
+      <c r="O34" s="37">
         <v>3.45</v>
       </c>
-      <c r="P34" s="36">
+      <c r="P34" s="37">
         <v>2.84</v>
       </c>
-      <c r="Q34" s="36">
+      <c r="Q34" s="37">
         <v>2.46</v>
       </c>
-      <c r="R34" s="36">
+      <c r="R34" s="37">
         <v>2.33</v>
       </c>
-      <c r="S34" s="36"/>
-      <c r="T34" s="36"/>
-      <c r="U34" s="36"/>
-      <c r="V34" s="36"/>
+      <c r="S34" s="37"/>
+      <c r="T34" s="37"/>
+      <c r="U34" s="37"/>
+      <c r="V34" s="37"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="32" t="s">
-        <v>288</v>
-      </c>
-      <c r="B35" s="36">
+      <c r="A35" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="B35" s="37">
         <v>0.0</v>
       </c>
-      <c r="C35" s="36">
+      <c r="C35" s="37">
         <v>0.0</v>
       </c>
-      <c r="D35" s="36">
+      <c r="D35" s="37">
         <v>0.0</v>
       </c>
-      <c r="E35" s="36">
+      <c r="E35" s="37">
         <v>0.0</v>
       </c>
-      <c r="F35" s="36">
+      <c r="F35" s="37">
         <v>0.0</v>
       </c>
-      <c r="G35" s="36">
+      <c r="G35" s="37">
         <v>0.0</v>
       </c>
-      <c r="H35" s="36">
+      <c r="H35" s="37">
         <v>2.36</v>
       </c>
-      <c r="I35" s="36">
+      <c r="I35" s="37">
         <v>0.0</v>
       </c>
-      <c r="J35" s="36">
+      <c r="J35" s="37">
         <v>7.5</v>
       </c>
-      <c r="K35" s="36">
+      <c r="K35" s="37">
         <v>8.84</v>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="37">
         <v>16.06</v>
       </c>
-      <c r="M35" s="36">
+      <c r="M35" s="37">
         <v>4.92</v>
       </c>
-      <c r="N35" s="36">
+      <c r="N35" s="37">
         <v>2.12</v>
       </c>
-      <c r="O35" s="36">
+      <c r="O35" s="37">
         <v>3.32</v>
       </c>
-      <c r="P35" s="36">
+      <c r="P35" s="37">
         <v>3.31</v>
       </c>
-      <c r="Q35" s="36">
+      <c r="Q35" s="37">
         <v>3.42</v>
       </c>
-      <c r="R35" s="36">
+      <c r="R35" s="37">
         <v>10.0</v>
       </c>
-      <c r="S35" s="36">
+      <c r="S35" s="37">
         <v>6.02</v>
       </c>
-      <c r="T35" s="36">
+      <c r="T35" s="37">
         <v>1.48</v>
       </c>
-      <c r="U35" s="36">
+      <c r="U35" s="37">
         <v>0.0</v>
       </c>
-      <c r="V35" s="36">
+      <c r="V35" s="37">
         <v>0.0</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="B36" s="36">
+      <c r="A36" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="B36" s="37">
         <v>0.0</v>
       </c>
-      <c r="C36" s="36">
+      <c r="C36" s="37">
         <v>0.0</v>
       </c>
-      <c r="D36" s="36">
+      <c r="D36" s="37">
         <v>1.15</v>
       </c>
-      <c r="E36" s="36">
+      <c r="E36" s="37">
         <v>0.87</v>
       </c>
-      <c r="F36" s="36">
+      <c r="F36" s="37">
         <v>2.94</v>
       </c>
-      <c r="G36" s="36">
+      <c r="G36" s="37">
         <v>4.68</v>
       </c>
-      <c r="H36" s="36">
+      <c r="H36" s="37">
         <v>6.5</v>
       </c>
-      <c r="I36" s="36">
+      <c r="I36" s="37">
         <v>7.2</v>
       </c>
-      <c r="J36" s="36">
+      <c r="J36" s="37">
         <v>8.09</v>
       </c>
-      <c r="K36" s="36">
+      <c r="K36" s="37">
         <v>7.5</v>
       </c>
-      <c r="L36" s="36">
+      <c r="L36" s="37">
         <v>5.89</v>
       </c>
-      <c r="M36" s="36">
+      <c r="M36" s="37">
         <v>3.43</v>
       </c>
-      <c r="N36" s="36">
+      <c r="N36" s="37">
         <v>4.1</v>
       </c>
-      <c r="O36" s="36">
+      <c r="O36" s="37">
         <v>4.93</v>
       </c>
-      <c r="P36" s="36">
+      <c r="P36" s="37">
         <v>4.06</v>
       </c>
-      <c r="Q36" s="36">
+      <c r="Q36" s="37">
         <v>3.51</v>
       </c>
-      <c r="R36" s="36">
+      <c r="R36" s="37">
         <v>3.33</v>
       </c>
-      <c r="S36" s="36"/>
-      <c r="T36" s="36"/>
-      <c r="U36" s="36"/>
-      <c r="V36" s="36"/>
+      <c r="S36" s="37"/>
+      <c r="T36" s="37"/>
+      <c r="U36" s="37"/>
+      <c r="V36" s="37"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="30" t="s">
-        <v>290</v>
-      </c>
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
-      <c r="I37" s="31"/>
-      <c r="J37" s="31"/>
-      <c r="K37" s="31"/>
-      <c r="L37" s="31"/>
-      <c r="M37" s="31"/>
-      <c r="N37" s="31"/>
-      <c r="O37" s="31"/>
-      <c r="P37" s="31"/>
-      <c r="Q37" s="31"/>
-      <c r="R37" s="31"/>
-      <c r="S37" s="31"/>
-      <c r="T37" s="31"/>
-      <c r="U37" s="31"/>
-      <c r="V37" s="31"/>
+      <c r="A37" s="31" t="s">
+        <v>291</v>
+      </c>
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="32"/>
+      <c r="L37" s="32"/>
+      <c r="M37" s="32"/>
+      <c r="N37" s="32"/>
+      <c r="O37" s="32"/>
+      <c r="P37" s="32"/>
+      <c r="Q37" s="32"/>
+      <c r="R37" s="32"/>
+      <c r="S37" s="32"/>
+      <c r="T37" s="32"/>
+      <c r="U37" s="32"/>
+      <c r="V37" s="32"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="32" t="s">
-        <v>291</v>
-      </c>
-      <c r="B38" s="34">
+      <c r="A38" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="B38" s="35">
         <v>4.16</v>
       </c>
-      <c r="C38" s="34">
+      <c r="C38" s="35">
         <v>3.32</v>
       </c>
-      <c r="D38" s="34">
+      <c r="D38" s="35">
         <v>6.15</v>
       </c>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="34">
+      <c r="E38" s="36"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="35">
         <v>1.4</v>
       </c>
-      <c r="H38" s="34">
+      <c r="H38" s="35">
         <v>2.52</v>
       </c>
-      <c r="I38" s="34">
+      <c r="I38" s="35">
         <v>1.77</v>
       </c>
-      <c r="J38" s="34">
+      <c r="J38" s="35">
         <v>2.32</v>
       </c>
-      <c r="K38" s="34">
+      <c r="K38" s="35">
         <v>2.38</v>
       </c>
-      <c r="L38" s="34">
+      <c r="L38" s="35">
         <v>1.16</v>
       </c>
-      <c r="M38" s="34">
+      <c r="M38" s="35">
         <v>1.28</v>
       </c>
-      <c r="N38" s="34">
+      <c r="N38" s="35">
         <v>1.15</v>
       </c>
-      <c r="O38" s="34">
+      <c r="O38" s="35">
         <v>1.18</v>
       </c>
-      <c r="P38" s="34">
+      <c r="P38" s="35">
         <v>1.73</v>
       </c>
-      <c r="Q38" s="34">
+      <c r="Q38" s="35">
         <v>1.83</v>
       </c>
-      <c r="R38" s="34">
+      <c r="R38" s="35">
         <v>1.58</v>
       </c>
-      <c r="S38" s="34">
+      <c r="S38" s="35">
         <v>3.7</v>
       </c>
-      <c r="T38" s="34">
+      <c r="T38" s="35">
         <v>5.67</v>
       </c>
-      <c r="U38" s="34">
+      <c r="U38" s="35">
         <v>4.25</v>
       </c>
-      <c r="V38" s="34">
+      <c r="V38" s="35">
         <v>2.08</v>
       </c>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="32" t="s">
-        <v>292</v>
-      </c>
-      <c r="B39" s="35"/>
-      <c r="C39" s="34">
+      <c r="A39" s="33" t="s">
+        <v>293</v>
+      </c>
+      <c r="B39" s="36"/>
+      <c r="C39" s="35">
         <v>9.3</v>
       </c>
-      <c r="D39" s="34">
+      <c r="D39" s="35">
         <v>4.51</v>
       </c>
-      <c r="E39" s="34">
+      <c r="E39" s="35">
         <v>2.91</v>
       </c>
-      <c r="F39" s="34">
+      <c r="F39" s="35">
         <v>2.48</v>
       </c>
-      <c r="G39" s="34">
+      <c r="G39" s="35">
         <v>2.13</v>
       </c>
-      <c r="H39" s="34">
+      <c r="H39" s="35">
         <v>1.99</v>
       </c>
-      <c r="I39" s="34">
+      <c r="I39" s="35">
         <v>1.77</v>
       </c>
-      <c r="J39" s="34">
+      <c r="J39" s="35">
         <v>1.64</v>
       </c>
-      <c r="K39" s="34">
+      <c r="K39" s="35">
         <v>1.44</v>
       </c>
-      <c r="L39" s="34">
+      <c r="L39" s="35">
         <v>1.29</v>
       </c>
-      <c r="M39" s="34">
+      <c r="M39" s="35">
         <v>1.43</v>
       </c>
-      <c r="N39" s="34">
+      <c r="N39" s="35">
         <v>1.48</v>
       </c>
-      <c r="O39" s="34">
+      <c r="O39" s="35">
         <v>1.88</v>
       </c>
-      <c r="P39" s="34">
+      <c r="P39" s="35">
         <v>2.61</v>
       </c>
-      <c r="Q39" s="34">
+      <c r="Q39" s="35">
         <v>3.09</v>
       </c>
-      <c r="R39" s="34">
+      <c r="R39" s="35">
         <v>3.51</v>
       </c>
-      <c r="S39" s="35"/>
-      <c r="T39" s="35"/>
-      <c r="U39" s="35"/>
-      <c r="V39" s="35"/>
+      <c r="S39" s="36"/>
+      <c r="T39" s="36"/>
+      <c r="U39" s="36"/>
+      <c r="V39" s="36"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="30" t="s">
-        <v>293</v>
-      </c>
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="31"/>
-      <c r="I40" s="31"/>
-      <c r="J40" s="31"/>
-      <c r="K40" s="31"/>
-      <c r="L40" s="31"/>
-      <c r="M40" s="31"/>
-      <c r="N40" s="31"/>
-      <c r="O40" s="31"/>
-      <c r="P40" s="31"/>
-      <c r="Q40" s="31"/>
-      <c r="R40" s="31"/>
-      <c r="S40" s="31"/>
-      <c r="T40" s="31"/>
-      <c r="U40" s="31"/>
-      <c r="V40" s="31"/>
+      <c r="A40" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="32"/>
+      <c r="K40" s="32"/>
+      <c r="L40" s="32"/>
+      <c r="M40" s="32"/>
+      <c r="N40" s="32"/>
+      <c r="O40" s="32"/>
+      <c r="P40" s="32"/>
+      <c r="Q40" s="32"/>
+      <c r="R40" s="32"/>
+      <c r="S40" s="32"/>
+      <c r="T40" s="32"/>
+      <c r="U40" s="32"/>
+      <c r="V40" s="32"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="32" t="s">
-        <v>294</v>
-      </c>
-      <c r="B41" s="35"/>
-      <c r="C41" s="35"/>
-      <c r="D41" s="35"/>
-      <c r="E41" s="35"/>
-      <c r="F41" s="35"/>
-      <c r="G41" s="35"/>
-      <c r="H41" s="35"/>
-      <c r="I41" s="35"/>
-      <c r="J41" s="34">
+      <c r="A41" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="B41" s="36"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="36"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="36"/>
+      <c r="J41" s="35">
         <v>6.67</v>
       </c>
-      <c r="K41" s="34">
+      <c r="K41" s="35">
         <v>5.43</v>
       </c>
-      <c r="L41" s="34">
+      <c r="L41" s="35">
         <v>2.59</v>
       </c>
-      <c r="M41" s="34">
+      <c r="M41" s="35">
         <v>3.65</v>
       </c>
-      <c r="N41" s="34">
+      <c r="N41" s="35">
         <v>3.14</v>
       </c>
-      <c r="O41" s="34">
+      <c r="O41" s="35">
         <v>3.01</v>
       </c>
-      <c r="P41" s="34">
+      <c r="P41" s="35">
         <v>5.27</v>
       </c>
-      <c r="Q41" s="34">
+      <c r="Q41" s="35">
         <v>5.89</v>
       </c>
-      <c r="R41" s="34">
+      <c r="R41" s="35">
         <v>4.62</v>
       </c>
-      <c r="S41" s="34">
+      <c r="S41" s="35">
         <v>14.79</v>
       </c>
-      <c r="T41" s="34">
+      <c r="T41" s="35">
         <v>7.59</v>
       </c>
-      <c r="U41" s="34">
+      <c r="U41" s="35">
         <v>6.85</v>
       </c>
-      <c r="V41" s="34">
+      <c r="V41" s="35">
         <v>5.84</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="32" t="s">
-        <v>295</v>
-      </c>
-      <c r="B42" s="35"/>
-      <c r="C42" s="35"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="35"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="35"/>
-      <c r="H42" s="34">
+      <c r="A42" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="B42" s="36"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="36"/>
+      <c r="H42" s="35">
         <v>22.13</v>
       </c>
-      <c r="I42" s="34">
+      <c r="I42" s="35">
         <v>6.08</v>
       </c>
-      <c r="J42" s="34">
+      <c r="J42" s="35">
         <v>4.18</v>
       </c>
-      <c r="K42" s="34">
+      <c r="K42" s="35">
         <v>3.59</v>
       </c>
-      <c r="L42" s="34">
+      <c r="L42" s="35">
         <v>3.42</v>
       </c>
-      <c r="M42" s="34">
+      <c r="M42" s="35">
         <v>4.1</v>
       </c>
-      <c r="N42" s="34">
+      <c r="N42" s="35">
         <v>4.26</v>
       </c>
-      <c r="O42" s="34">
+      <c r="O42" s="35">
         <v>5.7</v>
       </c>
-      <c r="P42" s="34">
+      <c r="P42" s="35">
         <v>7.0</v>
       </c>
-      <c r="Q42" s="34">
+      <c r="Q42" s="35">
         <v>7.4</v>
       </c>
-      <c r="R42" s="34">
+      <c r="R42" s="35">
         <v>7.71</v>
       </c>
-      <c r="S42" s="35"/>
-      <c r="T42" s="35"/>
-      <c r="U42" s="35"/>
-      <c r="V42" s="35"/>
+      <c r="S42" s="36"/>
+      <c r="T42" s="36"/>
+      <c r="U42" s="36"/>
+      <c r="V42" s="36"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="30" t="s">
-        <v>296</v>
-      </c>
-      <c r="B43" s="31"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="31"/>
-      <c r="H43" s="31"/>
-      <c r="I43" s="31"/>
-      <c r="J43" s="31"/>
-      <c r="K43" s="31"/>
-      <c r="L43" s="31"/>
-      <c r="M43" s="31"/>
-      <c r="N43" s="31"/>
-      <c r="O43" s="31"/>
-      <c r="P43" s="31"/>
-      <c r="Q43" s="31"/>
-      <c r="R43" s="31"/>
-      <c r="S43" s="31"/>
-      <c r="T43" s="31"/>
-      <c r="U43" s="31"/>
-      <c r="V43" s="31"/>
+      <c r="A43" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="B43" s="32"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32"/>
+      <c r="J43" s="32"/>
+      <c r="K43" s="32"/>
+      <c r="L43" s="32"/>
+      <c r="M43" s="32"/>
+      <c r="N43" s="32"/>
+      <c r="O43" s="32"/>
+      <c r="P43" s="32"/>
+      <c r="Q43" s="32"/>
+      <c r="R43" s="32"/>
+      <c r="S43" s="32"/>
+      <c r="T43" s="32"/>
+      <c r="U43" s="32"/>
+      <c r="V43" s="32"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="32" t="s">
-        <v>297</v>
-      </c>
-      <c r="B44" s="34">
+      <c r="A44" s="33" t="s">
+        <v>298</v>
+      </c>
+      <c r="B44" s="35">
         <v>0.21</v>
       </c>
-      <c r="C44" s="34">
+      <c r="C44" s="35">
         <v>0.28</v>
       </c>
-      <c r="D44" s="34">
+      <c r="D44" s="35">
         <v>0.32</v>
       </c>
-      <c r="E44" s="34">
+      <c r="E44" s="35">
         <v>0.79</v>
       </c>
-      <c r="F44" s="34">
+      <c r="F44" s="35">
         <v>0.18</v>
       </c>
-      <c r="G44" s="34">
+      <c r="G44" s="35">
         <v>0.11</v>
       </c>
-      <c r="H44" s="34">
+      <c r="H44" s="35">
         <v>0.2</v>
       </c>
-      <c r="I44" s="34">
+      <c r="I44" s="35">
         <v>0.25</v>
       </c>
-      <c r="J44" s="34">
+      <c r="J44" s="35">
         <v>0.34</v>
       </c>
-      <c r="K44" s="34">
+      <c r="K44" s="35">
         <v>0.39</v>
       </c>
-      <c r="L44" s="34">
+      <c r="L44" s="35">
         <v>0.22</v>
       </c>
-      <c r="M44" s="34">
+      <c r="M44" s="35">
         <v>0.22</v>
       </c>
-      <c r="N44" s="34">
+      <c r="N44" s="35">
         <v>0.18</v>
       </c>
-      <c r="O44" s="34">
+      <c r="O44" s="35">
         <v>0.21</v>
       </c>
-      <c r="P44" s="34">
+      <c r="P44" s="35">
         <v>0.33</v>
       </c>
-      <c r="Q44" s="34">
+      <c r="Q44" s="35">
         <v>0.53</v>
       </c>
-      <c r="R44" s="34">
+      <c r="R44" s="35">
         <v>0.2</v>
       </c>
-      <c r="S44" s="34">
+      <c r="S44" s="35">
         <v>0.75</v>
       </c>
-      <c r="T44" s="34">
+      <c r="T44" s="35">
         <v>1.18</v>
       </c>
-      <c r="U44" s="34">
+      <c r="U44" s="35">
         <v>0.74</v>
       </c>
-      <c r="V44" s="34">
+      <c r="V44" s="35">
         <v>0.23</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="32" t="s">
-        <v>298</v>
-      </c>
-      <c r="B45" s="34">
+      <c r="A45" s="33" t="s">
+        <v>299</v>
+      </c>
+      <c r="B45" s="35">
         <v>0.3</v>
       </c>
-      <c r="C45" s="34">
+      <c r="C45" s="35">
         <v>0.23</v>
       </c>
-      <c r="D45" s="34">
+      <c r="D45" s="35">
         <v>0.2</v>
       </c>
-      <c r="E45" s="34">
+      <c r="E45" s="35">
         <v>0.21</v>
       </c>
-      <c r="F45" s="34">
+      <c r="F45" s="35">
         <v>0.22</v>
       </c>
-      <c r="G45" s="34">
+      <c r="G45" s="35">
         <v>0.25</v>
       </c>
-      <c r="H45" s="34">
+      <c r="H45" s="35">
         <v>0.27</v>
       </c>
-      <c r="I45" s="34">
+      <c r="I45" s="35">
         <v>0.29</v>
       </c>
-      <c r="J45" s="34">
+      <c r="J45" s="35">
         <v>0.27</v>
       </c>
-      <c r="K45" s="34">
+      <c r="K45" s="35">
         <v>0.25</v>
       </c>
-      <c r="L45" s="34">
+      <c r="L45" s="35">
         <v>0.23</v>
       </c>
-      <c r="M45" s="34">
+      <c r="M45" s="35">
         <v>0.27</v>
       </c>
-      <c r="N45" s="34">
+      <c r="N45" s="35">
         <v>0.27</v>
       </c>
-      <c r="O45" s="34">
+      <c r="O45" s="35">
         <v>0.36</v>
       </c>
-      <c r="P45" s="34">
+      <c r="P45" s="35">
         <v>0.51</v>
       </c>
-      <c r="Q45" s="34">
+      <c r="Q45" s="35">
         <v>0.6</v>
       </c>
-      <c r="R45" s="34">
+      <c r="R45" s="35">
         <v>0.57</v>
       </c>
-      <c r="S45" s="35"/>
-      <c r="T45" s="35"/>
-      <c r="U45" s="35"/>
-      <c r="V45" s="35"/>
+      <c r="S45" s="36"/>
+      <c r="T45" s="36"/>
+      <c r="U45" s="36"/>
+      <c r="V45" s="36"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="30" t="s">
-        <v>299</v>
-      </c>
-      <c r="B46" s="31"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="31"/>
-      <c r="H46" s="31"/>
-      <c r="I46" s="31"/>
-      <c r="J46" s="31"/>
-      <c r="K46" s="31"/>
-      <c r="L46" s="31"/>
-      <c r="M46" s="31"/>
-      <c r="N46" s="31"/>
-      <c r="O46" s="31"/>
-      <c r="P46" s="31"/>
-      <c r="Q46" s="31"/>
-      <c r="R46" s="31"/>
-      <c r="S46" s="31"/>
-      <c r="T46" s="31"/>
-      <c r="U46" s="31"/>
-      <c r="V46" s="31"/>
+      <c r="A46" s="31" t="s">
+        <v>300</v>
+      </c>
+      <c r="B46" s="32"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="32"/>
+      <c r="K46" s="32"/>
+      <c r="L46" s="32"/>
+      <c r="M46" s="32"/>
+      <c r="N46" s="32"/>
+      <c r="O46" s="32"/>
+      <c r="P46" s="32"/>
+      <c r="Q46" s="32"/>
+      <c r="R46" s="32"/>
+      <c r="S46" s="32"/>
+      <c r="T46" s="32"/>
+      <c r="U46" s="32"/>
+      <c r="V46" s="32"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="32" t="s">
-        <v>300</v>
-      </c>
-      <c r="B47" s="34">
+      <c r="A47" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="B47" s="35">
         <v>3.55</v>
       </c>
-      <c r="C47" s="34">
+      <c r="C47" s="35">
         <v>19.03</v>
       </c>
-      <c r="D47" s="34">
+      <c r="D47" s="35">
         <v>3.3</v>
       </c>
-      <c r="E47" s="34">
+      <c r="E47" s="35">
         <v>3.6</v>
       </c>
-      <c r="F47" s="35"/>
-      <c r="G47" s="34">
+      <c r="F47" s="36"/>
+      <c r="G47" s="35">
         <v>1.96</v>
       </c>
-      <c r="H47" s="35"/>
-      <c r="I47" s="35"/>
-      <c r="J47" s="35"/>
-      <c r="K47" s="34">
+      <c r="H47" s="36"/>
+      <c r="I47" s="36"/>
+      <c r="J47" s="36"/>
+      <c r="K47" s="35">
         <v>4.6</v>
       </c>
-      <c r="L47" s="34">
+      <c r="L47" s="35">
         <v>12.09</v>
       </c>
-      <c r="M47" s="35"/>
-      <c r="N47" s="34">
+      <c r="M47" s="36"/>
+      <c r="N47" s="35">
         <v>3.92</v>
       </c>
-      <c r="O47" s="35"/>
-      <c r="P47" s="34">
+      <c r="O47" s="36"/>
+      <c r="P47" s="35">
         <v>17.79</v>
       </c>
-      <c r="Q47" s="34">
+      <c r="Q47" s="35">
         <v>2.99</v>
       </c>
-      <c r="R47" s="34">
+      <c r="R47" s="35">
         <v>3.06</v>
       </c>
-      <c r="S47" s="34">
+      <c r="S47" s="35">
         <v>17.2</v>
       </c>
-      <c r="T47" s="34">
+      <c r="T47" s="35">
         <v>13.84</v>
       </c>
-      <c r="U47" s="34">
+      <c r="U47" s="35">
         <v>5.2</v>
       </c>
-      <c r="V47" s="34">
+      <c r="V47" s="35">
         <v>5.43</v>
       </c>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="32" t="s">
-        <v>301</v>
-      </c>
-      <c r="B48" s="34">
+      <c r="A48" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="B48" s="35">
         <v>13.62</v>
       </c>
-      <c r="C48" s="34">
+      <c r="C48" s="35">
         <v>6.57</v>
       </c>
-      <c r="D48" s="35"/>
-      <c r="E48" s="35"/>
-      <c r="F48" s="35"/>
-      <c r="G48" s="35"/>
-      <c r="H48" s="35"/>
-      <c r="I48" s="34">
+      <c r="D48" s="36"/>
+      <c r="E48" s="36"/>
+      <c r="F48" s="36"/>
+      <c r="G48" s="36"/>
+      <c r="H48" s="36"/>
+      <c r="I48" s="35">
         <v>35.09</v>
       </c>
-      <c r="J48" s="34">
+      <c r="J48" s="35">
         <v>12.12</v>
       </c>
-      <c r="K48" s="34">
+      <c r="K48" s="35">
         <v>17.26</v>
       </c>
-      <c r="L48" s="35"/>
-      <c r="M48" s="34">
+      <c r="L48" s="36"/>
+      <c r="M48" s="35">
         <v>15.04</v>
       </c>
-      <c r="N48" s="34">
+      <c r="N48" s="35">
         <v>8.14</v>
       </c>
-      <c r="O48" s="34">
+      <c r="O48" s="35">
         <v>11.74</v>
       </c>
-      <c r="P48" s="34">
+      <c r="P48" s="35">
         <v>7.09</v>
       </c>
-      <c r="Q48" s="34">
+      <c r="Q48" s="35">
         <v>6.08</v>
       </c>
-      <c r="R48" s="34">
+      <c r="R48" s="35">
         <v>7.79</v>
       </c>
-      <c r="S48" s="35"/>
-      <c r="T48" s="35"/>
-      <c r="U48" s="35"/>
-      <c r="V48" s="35"/>
+      <c r="S48" s="36"/>
+      <c r="T48" s="36"/>
+      <c r="U48" s="36"/>
+      <c r="V48" s="36"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="30" t="s">
-        <v>302</v>
-      </c>
-      <c r="B49" s="31"/>
-      <c r="C49" s="31"/>
-      <c r="D49" s="31"/>
-      <c r="E49" s="31"/>
-      <c r="F49" s="31"/>
-      <c r="G49" s="31"/>
-      <c r="H49" s="31"/>
-      <c r="I49" s="31"/>
-      <c r="J49" s="31"/>
-      <c r="K49" s="31"/>
-      <c r="L49" s="31"/>
-      <c r="M49" s="31"/>
-      <c r="N49" s="31"/>
-      <c r="O49" s="31"/>
-      <c r="P49" s="31"/>
-      <c r="Q49" s="31"/>
-      <c r="R49" s="31"/>
-      <c r="S49" s="31"/>
-      <c r="T49" s="31"/>
-      <c r="U49" s="31"/>
-      <c r="V49" s="31"/>
+      <c r="A49" s="31" t="s">
+        <v>303</v>
+      </c>
+      <c r="B49" s="32"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
+      <c r="J49" s="32"/>
+      <c r="K49" s="32"/>
+      <c r="L49" s="32"/>
+      <c r="M49" s="32"/>
+      <c r="N49" s="32"/>
+      <c r="O49" s="32"/>
+      <c r="P49" s="32"/>
+      <c r="Q49" s="32"/>
+      <c r="R49" s="32"/>
+      <c r="S49" s="32"/>
+      <c r="T49" s="32"/>
+      <c r="U49" s="32"/>
+      <c r="V49" s="32"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="32" t="s">
-        <v>303</v>
-      </c>
-      <c r="B50" s="34">
+      <c r="A50" s="33" t="s">
+        <v>304</v>
+      </c>
+      <c r="B50" s="35">
         <v>8.65</v>
       </c>
-      <c r="C50" s="34">
+      <c r="C50" s="35">
         <v>2.62</v>
       </c>
-      <c r="D50" s="34">
+      <c r="D50" s="35">
         <v>2.59</v>
       </c>
-      <c r="E50" s="34">
+      <c r="E50" s="35">
         <v>2.89</v>
       </c>
-      <c r="F50" s="35"/>
-      <c r="G50" s="34">
+      <c r="F50" s="36"/>
+      <c r="G50" s="35">
         <v>11.76</v>
       </c>
-      <c r="H50" s="35"/>
-      <c r="I50" s="34">
+      <c r="H50" s="36"/>
+      <c r="I50" s="35">
         <v>6.99</v>
       </c>
-      <c r="J50" s="34">
+      <c r="J50" s="35">
         <v>34.33</v>
       </c>
-      <c r="K50" s="34">
+      <c r="K50" s="35">
         <v>8.06</v>
       </c>
-      <c r="L50" s="34">
+      <c r="L50" s="35">
         <v>3.02</v>
       </c>
-      <c r="M50" s="34">
+      <c r="M50" s="35">
         <v>11.26</v>
       </c>
-      <c r="N50" s="34">
+      <c r="N50" s="35">
         <v>8.59</v>
       </c>
-      <c r="O50" s="34">
+      <c r="O50" s="35">
         <v>6.34</v>
       </c>
-      <c r="P50" s="34">
+      <c r="P50" s="35">
         <v>8.11</v>
       </c>
-      <c r="Q50" s="35"/>
-      <c r="R50" s="34">
+      <c r="Q50" s="36"/>
+      <c r="R50" s="35">
         <v>4.9</v>
       </c>
-      <c r="S50" s="34">
+      <c r="S50" s="35">
         <v>10.18</v>
       </c>
-      <c r="T50" s="34">
+      <c r="T50" s="35">
         <v>14.18</v>
       </c>
-      <c r="U50" s="34">
+      <c r="U50" s="35">
         <v>10.38</v>
       </c>
-      <c r="V50" s="34">
+      <c r="V50" s="35">
         <v>45.64</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="32" t="s">
-        <v>304</v>
-      </c>
-      <c r="B51" s="34">
+      <c r="A51" s="33" t="s">
+        <v>305</v>
+      </c>
+      <c r="B51" s="35">
         <v>67.61</v>
       </c>
-      <c r="C51" s="34">
+      <c r="C51" s="35">
         <v>57.59</v>
       </c>
-      <c r="D51" s="35"/>
-      <c r="E51" s="35"/>
-      <c r="F51" s="35"/>
-      <c r="G51" s="34">
+      <c r="D51" s="36"/>
+      <c r="E51" s="36"/>
+      <c r="F51" s="36"/>
+      <c r="G51" s="35">
         <v>18.05</v>
       </c>
-      <c r="H51" s="34">
+      <c r="H51" s="35">
         <v>11.17</v>
       </c>
-      <c r="I51" s="34">
+      <c r="I51" s="35">
         <v>7.65</v>
       </c>
-      <c r="J51" s="34">
+      <c r="J51" s="35">
         <v>7.94</v>
       </c>
-      <c r="K51" s="34">
+      <c r="K51" s="35">
         <v>6.34</v>
       </c>
-      <c r="L51" s="34">
+      <c r="L51" s="35">
         <v>6.17</v>
       </c>
-      <c r="M51" s="35"/>
-      <c r="N51" s="35"/>
-      <c r="O51" s="35"/>
-      <c r="P51" s="35"/>
-      <c r="Q51" s="35"/>
-      <c r="R51" s="34">
+      <c r="M51" s="36"/>
+      <c r="N51" s="36"/>
+      <c r="O51" s="36"/>
+      <c r="P51" s="36"/>
+      <c r="Q51" s="36"/>
+      <c r="R51" s="35">
         <v>10.44</v>
       </c>
-      <c r="S51" s="35"/>
-      <c r="T51" s="35"/>
-      <c r="U51" s="35"/>
-      <c r="V51" s="35"/>
+      <c r="S51" s="36"/>
+      <c r="T51" s="36"/>
+      <c r="U51" s="36"/>
+      <c r="V51" s="36"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="30" t="s">
-        <v>305</v>
-      </c>
-      <c r="B52" s="31"/>
-      <c r="C52" s="31"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="31"/>
-      <c r="G52" s="31"/>
-      <c r="H52" s="31"/>
-      <c r="I52" s="31"/>
-      <c r="J52" s="31"/>
-      <c r="K52" s="31"/>
-      <c r="L52" s="31"/>
-      <c r="M52" s="31"/>
-      <c r="N52" s="31"/>
-      <c r="O52" s="31"/>
-      <c r="P52" s="31"/>
-      <c r="Q52" s="31"/>
-      <c r="R52" s="31"/>
-      <c r="S52" s="31"/>
-      <c r="T52" s="31"/>
-      <c r="U52" s="31"/>
-      <c r="V52" s="31"/>
+      <c r="A52" s="31" t="s">
+        <v>306</v>
+      </c>
+      <c r="B52" s="32"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="32"/>
+      <c r="I52" s="32"/>
+      <c r="J52" s="32"/>
+      <c r="K52" s="32"/>
+      <c r="L52" s="32"/>
+      <c r="M52" s="32"/>
+      <c r="N52" s="32"/>
+      <c r="O52" s="32"/>
+      <c r="P52" s="32"/>
+      <c r="Q52" s="32"/>
+      <c r="R52" s="32"/>
+      <c r="S52" s="32"/>
+      <c r="T52" s="32"/>
+      <c r="U52" s="32"/>
+      <c r="V52" s="32"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="32" t="s">
-        <v>306</v>
-      </c>
-      <c r="B53" s="35"/>
-      <c r="C53" s="34">
+      <c r="A53" s="33" t="s">
+        <v>307</v>
+      </c>
+      <c r="B53" s="36"/>
+      <c r="C53" s="35">
         <v>6.5</v>
       </c>
-      <c r="D53" s="34">
+      <c r="D53" s="35">
         <v>6.03</v>
       </c>
-      <c r="E53" s="34">
+      <c r="E53" s="35">
         <v>6.59</v>
       </c>
-      <c r="F53" s="35"/>
-      <c r="G53" s="35"/>
-      <c r="H53" s="35"/>
-      <c r="I53" s="34">
+      <c r="F53" s="36"/>
+      <c r="G53" s="36"/>
+      <c r="H53" s="36"/>
+      <c r="I53" s="35">
         <v>11.73</v>
       </c>
-      <c r="J53" s="35"/>
-      <c r="K53" s="34">
+      <c r="J53" s="36"/>
+      <c r="K53" s="35">
         <v>12.3</v>
       </c>
-      <c r="L53" s="34">
+      <c r="L53" s="35">
         <v>3.96</v>
       </c>
-      <c r="M53" s="34">
+      <c r="M53" s="35">
         <v>87.33</v>
       </c>
-      <c r="N53" s="34">
+      <c r="N53" s="35">
         <v>27.01</v>
       </c>
-      <c r="O53" s="34">
+      <c r="O53" s="35">
         <v>23.6</v>
       </c>
-      <c r="P53" s="34">
+      <c r="P53" s="35">
         <v>21.64</v>
       </c>
-      <c r="Q53" s="34">
+      <c r="Q53" s="35">
         <v>16.18</v>
       </c>
-      <c r="R53" s="34">
+      <c r="R53" s="35">
         <v>7.78</v>
       </c>
-      <c r="S53" s="34">
+      <c r="S53" s="35">
         <v>11.01</v>
       </c>
-      <c r="T53" s="34">
+      <c r="T53" s="35">
         <v>15.16</v>
       </c>
-      <c r="U53" s="34">
+      <c r="U53" s="35">
         <v>11.39</v>
       </c>
-      <c r="V53" s="35"/>
+      <c r="V53" s="36"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="32" t="s">
-        <v>307</v>
-      </c>
-      <c r="B54" s="35"/>
-      <c r="C54" s="35"/>
-      <c r="D54" s="35"/>
-      <c r="E54" s="35"/>
-      <c r="F54" s="35"/>
-      <c r="G54" s="35"/>
-      <c r="H54" s="34">
+      <c r="A54" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="B54" s="36"/>
+      <c r="C54" s="36"/>
+      <c r="D54" s="36"/>
+      <c r="E54" s="36"/>
+      <c r="F54" s="36"/>
+      <c r="G54" s="36"/>
+      <c r="H54" s="35">
         <v>32.53</v>
       </c>
-      <c r="I54" s="34">
+      <c r="I54" s="35">
         <v>13.7</v>
       </c>
-      <c r="J54" s="34">
+      <c r="J54" s="35">
         <v>15.33</v>
       </c>
-      <c r="K54" s="34">
+      <c r="K54" s="35">
         <v>11.64</v>
       </c>
-      <c r="L54" s="34">
+      <c r="L54" s="35">
         <v>12.91</v>
       </c>
-      <c r="M54" s="34">
+      <c r="M54" s="35">
         <v>23.84</v>
       </c>
-      <c r="N54" s="34">
+      <c r="N54" s="35">
         <v>16.69</v>
       </c>
-      <c r="O54" s="34">
+      <c r="O54" s="35">
         <v>13.9</v>
       </c>
-      <c r="P54" s="34">
+      <c r="P54" s="35">
         <v>13.58</v>
       </c>
-      <c r="Q54" s="34">
+      <c r="Q54" s="35">
         <v>12.36</v>
       </c>
-      <c r="R54" s="34">
+      <c r="R54" s="35">
         <v>12.55</v>
       </c>
-      <c r="S54" s="35"/>
-      <c r="T54" s="35"/>
-      <c r="U54" s="35"/>
-      <c r="V54" s="35"/>
+      <c r="S54" s="36"/>
+      <c r="T54" s="36"/>
+      <c r="U54" s="36"/>
+      <c r="V54" s="36"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="30" t="s">
-        <v>308</v>
-      </c>
-      <c r="B55" s="31"/>
-      <c r="C55" s="31"/>
-      <c r="D55" s="31"/>
-      <c r="E55" s="31"/>
-      <c r="F55" s="31"/>
-      <c r="G55" s="31"/>
-      <c r="H55" s="31"/>
-      <c r="I55" s="31"/>
-      <c r="J55" s="31"/>
-      <c r="K55" s="31"/>
-      <c r="L55" s="31"/>
-      <c r="M55" s="31"/>
-      <c r="N55" s="31"/>
-      <c r="O55" s="31"/>
-      <c r="P55" s="31"/>
-      <c r="Q55" s="31"/>
-      <c r="R55" s="31"/>
-      <c r="S55" s="31"/>
-      <c r="T55" s="31"/>
-      <c r="U55" s="31"/>
-      <c r="V55" s="31"/>
+      <c r="A55" s="31" t="s">
+        <v>309</v>
+      </c>
+      <c r="B55" s="32"/>
+      <c r="C55" s="32"/>
+      <c r="D55" s="32"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="32"/>
+      <c r="J55" s="32"/>
+      <c r="K55" s="32"/>
+      <c r="L55" s="32"/>
+      <c r="M55" s="32"/>
+      <c r="N55" s="32"/>
+      <c r="O55" s="32"/>
+      <c r="P55" s="32"/>
+      <c r="Q55" s="32"/>
+      <c r="R55" s="32"/>
+      <c r="S55" s="32"/>
+      <c r="T55" s="32"/>
+      <c r="U55" s="32"/>
+      <c r="V55" s="32"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="32" t="s">
-        <v>309</v>
-      </c>
-      <c r="B56" s="35"/>
-      <c r="C56" s="34">
+      <c r="A56" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="B56" s="36"/>
+      <c r="C56" s="35">
         <v>6.5</v>
       </c>
-      <c r="D56" s="34">
+      <c r="D56" s="35">
         <v>26.35</v>
       </c>
-      <c r="E56" s="35"/>
-      <c r="F56" s="35"/>
-      <c r="G56" s="35"/>
-      <c r="H56" s="35"/>
-      <c r="I56" s="34">
+      <c r="E56" s="36"/>
+      <c r="F56" s="36"/>
+      <c r="G56" s="36"/>
+      <c r="H56" s="36"/>
+      <c r="I56" s="35">
         <v>11.73</v>
       </c>
-      <c r="J56" s="35"/>
-      <c r="K56" s="34">
+      <c r="J56" s="36"/>
+      <c r="K56" s="35">
         <v>12.3</v>
       </c>
-      <c r="L56" s="34">
+      <c r="L56" s="35">
         <v>3.96</v>
       </c>
-      <c r="M56" s="34">
+      <c r="M56" s="35">
         <v>16.83</v>
       </c>
-      <c r="N56" s="34">
+      <c r="N56" s="35">
         <v>11.38</v>
       </c>
-      <c r="O56" s="34">
+      <c r="O56" s="35">
         <v>11.1</v>
       </c>
-      <c r="P56" s="34">
+      <c r="P56" s="35">
         <v>12.81</v>
       </c>
-      <c r="Q56" s="34">
+      <c r="Q56" s="35">
         <v>12.52</v>
       </c>
-      <c r="R56" s="34">
+      <c r="R56" s="35">
         <v>5.84</v>
       </c>
-      <c r="S56" s="34">
+      <c r="S56" s="35">
         <v>10.28</v>
       </c>
-      <c r="T56" s="34">
+      <c r="T56" s="35">
         <v>14.51</v>
       </c>
-      <c r="U56" s="34">
+      <c r="U56" s="35">
         <v>10.71</v>
       </c>
-      <c r="V56" s="33">
+      <c r="V56" s="34">
         <v>125.89</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="32" t="s">
-        <v>310</v>
-      </c>
-      <c r="B57" s="35"/>
-      <c r="C57" s="34">
+      <c r="A57" s="33" t="s">
+        <v>311</v>
+      </c>
+      <c r="B57" s="36"/>
+      <c r="C57" s="35">
         <v>9.3</v>
       </c>
-      <c r="D57" s="34">
+      <c r="D57" s="35">
         <v>4.51</v>
       </c>
-      <c r="E57" s="34">
+      <c r="E57" s="35">
         <v>2.91</v>
       </c>
-      <c r="F57" s="34">
+      <c r="F57" s="35">
         <v>2.48</v>
       </c>
-      <c r="G57" s="34">
+      <c r="G57" s="35">
         <v>2.13</v>
       </c>
-      <c r="H57" s="34">
+      <c r="H57" s="35">
         <v>1.99</v>
       </c>
-      <c r="I57" s="34">
+      <c r="I57" s="35">
         <v>1.77</v>
       </c>
-      <c r="J57" s="34">
+      <c r="J57" s="35">
         <v>1.64</v>
       </c>
-      <c r="K57" s="34">
+      <c r="K57" s="35">
         <v>1.44</v>
       </c>
-      <c r="L57" s="34">
+      <c r="L57" s="35">
         <v>1.29</v>
       </c>
-      <c r="M57" s="34">
+      <c r="M57" s="35">
         <v>1.43</v>
       </c>
-      <c r="N57" s="34">
+      <c r="N57" s="35">
         <v>1.48</v>
       </c>
-      <c r="O57" s="34">
+      <c r="O57" s="35">
         <v>1.88</v>
       </c>
-      <c r="P57" s="34">
+      <c r="P57" s="35">
         <v>2.61</v>
       </c>
-      <c r="Q57" s="34">
+      <c r="Q57" s="35">
         <v>3.09</v>
       </c>
-      <c r="R57" s="34">
+      <c r="R57" s="35">
         <v>3.51</v>
       </c>
-      <c r="S57" s="35"/>
-      <c r="T57" s="35"/>
-      <c r="U57" s="35"/>
-      <c r="V57" s="35"/>
+      <c r="S57" s="36"/>
+      <c r="T57" s="36"/>
+      <c r="U57" s="36"/>
+      <c r="V57" s="36"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="30" t="s">
-        <v>311</v>
-      </c>
-      <c r="B58" s="31"/>
-      <c r="C58" s="31"/>
-      <c r="D58" s="31"/>
-      <c r="E58" s="31"/>
-      <c r="F58" s="31"/>
-      <c r="G58" s="31"/>
-      <c r="H58" s="31"/>
-      <c r="I58" s="31"/>
-      <c r="J58" s="31"/>
-      <c r="K58" s="31"/>
-      <c r="L58" s="31"/>
-      <c r="M58" s="31"/>
-      <c r="N58" s="31"/>
-      <c r="O58" s="31"/>
-      <c r="P58" s="31"/>
-      <c r="Q58" s="31"/>
-      <c r="R58" s="31"/>
-      <c r="S58" s="31"/>
-      <c r="T58" s="31"/>
-      <c r="U58" s="31"/>
-      <c r="V58" s="31"/>
+      <c r="A58" s="31" t="s">
+        <v>312</v>
+      </c>
+      <c r="B58" s="32"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="32"/>
+      <c r="I58" s="32"/>
+      <c r="J58" s="32"/>
+      <c r="K58" s="32"/>
+      <c r="L58" s="32"/>
+      <c r="M58" s="32"/>
+      <c r="N58" s="32"/>
+      <c r="O58" s="32"/>
+      <c r="P58" s="32"/>
+      <c r="Q58" s="32"/>
+      <c r="R58" s="32"/>
+      <c r="S58" s="32"/>
+      <c r="T58" s="32"/>
+      <c r="U58" s="32"/>
+      <c r="V58" s="32"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="32" t="s">
-        <v>312</v>
-      </c>
-      <c r="B59" s="35"/>
-      <c r="C59" s="34">
+      <c r="A59" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="B59" s="36"/>
+      <c r="C59" s="35">
         <v>1.42</v>
       </c>
-      <c r="D59" s="38">
+      <c r="D59" s="39">
         <v>-0.41</v>
       </c>
-      <c r="E59" s="34">
+      <c r="E59" s="35">
         <v>0.06</v>
       </c>
-      <c r="F59" s="35"/>
-      <c r="G59" s="35"/>
-      <c r="H59" s="35"/>
-      <c r="I59" s="34">
+      <c r="F59" s="36"/>
+      <c r="G59" s="36"/>
+      <c r="H59" s="36"/>
+      <c r="I59" s="35">
         <v>0.03</v>
       </c>
-      <c r="J59" s="35"/>
-      <c r="K59" s="38">
+      <c r="J59" s="36"/>
+      <c r="K59" s="39">
         <v>-0.35</v>
       </c>
-      <c r="L59" s="35">
+      <c r="L59" s="36">
         <v>0.0</v>
       </c>
-      <c r="M59" s="38">
+      <c r="M59" s="39">
         <v>-1.31</v>
       </c>
-      <c r="N59" s="38">
+      <c r="N59" s="39">
         <v>-1.96</v>
       </c>
-      <c r="O59" s="38">
+      <c r="O59" s="39">
         <v>-0.64</v>
       </c>
-      <c r="P59" s="38">
+      <c r="P59" s="39">
         <v>-0.72</v>
       </c>
-      <c r="Q59" s="38">
+      <c r="Q59" s="39">
         <v>-1.54</v>
       </c>
-      <c r="R59" s="38">
+      <c r="R59" s="39">
         <v>-0.21</v>
       </c>
-      <c r="S59" s="34">
+      <c r="S59" s="35">
         <v>7.7</v>
       </c>
-      <c r="T59" s="34">
+      <c r="T59" s="35">
         <v>0.37</v>
       </c>
-      <c r="U59" s="35">
+      <c r="U59" s="36">
         <v>0.0</v>
       </c>
-      <c r="V59" s="35"/>
+      <c r="V59" s="36"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="32" t="s">
-        <v>313</v>
-      </c>
-      <c r="B60" s="35"/>
-      <c r="C60" s="35"/>
-      <c r="D60" s="35"/>
-      <c r="E60" s="35"/>
-      <c r="F60" s="35"/>
-      <c r="G60" s="35"/>
-      <c r="H60" s="35"/>
-      <c r="I60" s="34">
+      <c r="A60" s="33" t="s">
+        <v>314</v>
+      </c>
+      <c r="B60" s="36"/>
+      <c r="C60" s="36"/>
+      <c r="D60" s="36"/>
+      <c r="E60" s="36"/>
+      <c r="F60" s="36"/>
+      <c r="G60" s="36"/>
+      <c r="H60" s="36"/>
+      <c r="I60" s="35">
         <v>0.46</v>
       </c>
-      <c r="J60" s="35"/>
-      <c r="K60" s="34">
+      <c r="J60" s="36"/>
+      <c r="K60" s="35">
         <v>0.54</v>
       </c>
-      <c r="L60" s="34">
+      <c r="L60" s="35">
         <v>0.55</v>
       </c>
-      <c r="M60" s="38">
+      <c r="M60" s="39">
         <v>-0.68</v>
       </c>
-      <c r="N60" s="38">
+      <c r="N60" s="39">
         <v>-0.63</v>
       </c>
-      <c r="O60" s="38">
+      <c r="O60" s="39">
         <v>-0.58</v>
       </c>
-      <c r="P60" s="38">
+      <c r="P60" s="39">
         <v>-1.25</v>
       </c>
-      <c r="Q60" s="35"/>
-      <c r="R60" s="35"/>
-      <c r="S60" s="35"/>
-      <c r="T60" s="35"/>
-      <c r="U60" s="35"/>
-      <c r="V60" s="35"/>
+      <c r="Q60" s="36"/>
+      <c r="R60" s="36"/>
+      <c r="S60" s="36"/>
+      <c r="T60" s="36"/>
+      <c r="U60" s="36"/>
+      <c r="V60" s="36"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="30" t="s">
-        <v>314</v>
-      </c>
-      <c r="B61" s="31"/>
-      <c r="C61" s="31"/>
-      <c r="D61" s="31"/>
-      <c r="E61" s="31"/>
-      <c r="F61" s="31"/>
-      <c r="G61" s="31"/>
-      <c r="H61" s="31"/>
-      <c r="I61" s="31"/>
-      <c r="J61" s="31"/>
-      <c r="K61" s="31"/>
-      <c r="L61" s="31"/>
-      <c r="M61" s="31"/>
-      <c r="N61" s="31"/>
-      <c r="O61" s="31"/>
-      <c r="P61" s="31"/>
-      <c r="Q61" s="31"/>
-      <c r="R61" s="31"/>
-      <c r="S61" s="31"/>
-      <c r="T61" s="31"/>
-      <c r="U61" s="31"/>
-      <c r="V61" s="31"/>
+      <c r="A61" s="31" t="s">
+        <v>315</v>
+      </c>
+      <c r="B61" s="32"/>
+      <c r="C61" s="32"/>
+      <c r="D61" s="32"/>
+      <c r="E61" s="32"/>
+      <c r="F61" s="32"/>
+      <c r="G61" s="32"/>
+      <c r="H61" s="32"/>
+      <c r="I61" s="32"/>
+      <c r="J61" s="32"/>
+      <c r="K61" s="32"/>
+      <c r="L61" s="32"/>
+      <c r="M61" s="32"/>
+      <c r="N61" s="32"/>
+      <c r="O61" s="32"/>
+      <c r="P61" s="32"/>
+      <c r="Q61" s="32"/>
+      <c r="R61" s="32"/>
+      <c r="S61" s="32"/>
+      <c r="T61" s="32"/>
+      <c r="U61" s="32"/>
+      <c r="V61" s="32"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="32" t="s">
-        <v>315</v>
-      </c>
-      <c r="B62" s="34">
+      <c r="A62" s="33" t="s">
+        <v>316</v>
+      </c>
+      <c r="B62" s="35">
         <v>0.66</v>
       </c>
-      <c r="C62" s="34">
+      <c r="C62" s="35">
         <v>0.73</v>
       </c>
-      <c r="D62" s="34">
+      <c r="D62" s="35">
         <v>0.7</v>
       </c>
-      <c r="E62" s="34">
+      <c r="E62" s="35">
         <v>1.79</v>
       </c>
-      <c r="F62" s="34">
+      <c r="F62" s="35">
         <v>1.97</v>
       </c>
-      <c r="G62" s="34">
+      <c r="G62" s="35">
         <v>0.71</v>
       </c>
-      <c r="H62" s="34">
+      <c r="H62" s="35">
         <v>0.78</v>
       </c>
-      <c r="I62" s="34">
+      <c r="I62" s="35">
         <v>0.2</v>
       </c>
-      <c r="J62" s="34">
+      <c r="J62" s="35">
         <v>0.53</v>
       </c>
-      <c r="K62" s="34">
+      <c r="K62" s="35">
         <v>0.21</v>
       </c>
-      <c r="L62" s="34">
+      <c r="L62" s="35">
         <v>0.08</v>
       </c>
-      <c r="M62" s="34">
+      <c r="M62" s="35">
         <v>0.18</v>
       </c>
-      <c r="N62" s="34">
+      <c r="N62" s="35">
         <v>0.11</v>
       </c>
-      <c r="O62" s="34">
+      <c r="O62" s="35">
         <v>0.18</v>
       </c>
-      <c r="P62" s="34">
+      <c r="P62" s="35">
         <v>0.19</v>
       </c>
-      <c r="Q62" s="34">
+      <c r="Q62" s="35">
         <v>0.27</v>
       </c>
-      <c r="R62" s="34">
+      <c r="R62" s="35">
         <v>0.1</v>
       </c>
-      <c r="S62" s="34">
+      <c r="S62" s="35">
         <v>0.67</v>
       </c>
-      <c r="T62" s="34">
+      <c r="T62" s="35">
         <v>0.91</v>
       </c>
-      <c r="U62" s="34">
+      <c r="U62" s="35">
         <v>0.51</v>
       </c>
-      <c r="V62" s="34">
+      <c r="V62" s="35">
         <v>0.15</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="32" t="s">
-        <v>316</v>
-      </c>
-      <c r="B63" s="34">
+      <c r="A63" s="33" t="s">
+        <v>317</v>
+      </c>
+      <c r="B63" s="35">
         <v>0.93</v>
       </c>
-      <c r="C63" s="34">
+      <c r="C63" s="35">
         <v>0.95</v>
       </c>
-      <c r="D63" s="34">
+      <c r="D63" s="35">
         <v>0.96</v>
       </c>
-      <c r="E63" s="34">
+      <c r="E63" s="35">
         <v>0.82</v>
       </c>
-      <c r="F63" s="34">
+      <c r="F63" s="35">
         <v>0.67</v>
       </c>
-      <c r="G63" s="34">
+      <c r="G63" s="35">
         <v>0.49</v>
       </c>
-      <c r="H63" s="34">
+      <c r="H63" s="35">
         <v>0.38</v>
       </c>
-      <c r="I63" s="34">
+      <c r="I63" s="35">
         <v>0.24</v>
       </c>
-      <c r="J63" s="34">
+      <c r="J63" s="35">
         <v>0.22</v>
       </c>
-      <c r="K63" s="34">
+      <c r="K63" s="35">
         <v>0.15</v>
       </c>
-      <c r="L63" s="34">
+      <c r="L63" s="35">
         <v>0.14</v>
       </c>
-      <c r="M63" s="34">
+      <c r="M63" s="35">
         <v>0.18</v>
       </c>
-      <c r="N63" s="34">
+      <c r="N63" s="35">
         <v>0.16</v>
       </c>
-      <c r="O63" s="34">
+      <c r="O63" s="35">
         <v>0.24</v>
       </c>
-      <c r="P63" s="34">
+      <c r="P63" s="35">
         <v>0.33</v>
       </c>
-      <c r="Q63" s="34">
+      <c r="Q63" s="35">
         <v>0.41</v>
       </c>
-      <c r="R63" s="34">
+      <c r="R63" s="35">
         <v>0.42</v>
       </c>
-      <c r="S63" s="35"/>
-      <c r="T63" s="35"/>
-      <c r="U63" s="35"/>
-      <c r="V63" s="35"/>
+      <c r="S63" s="36"/>
+      <c r="T63" s="36"/>
+      <c r="U63" s="36"/>
+      <c r="V63" s="36"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="30" t="s">
-        <v>317</v>
-      </c>
-      <c r="B64" s="31"/>
-      <c r="C64" s="31"/>
-      <c r="D64" s="31"/>
-      <c r="E64" s="31"/>
-      <c r="F64" s="31"/>
-      <c r="G64" s="31"/>
-      <c r="H64" s="31"/>
-      <c r="I64" s="31"/>
-      <c r="J64" s="31"/>
-      <c r="K64" s="31"/>
-      <c r="L64" s="31"/>
-      <c r="M64" s="31"/>
-      <c r="N64" s="31"/>
-      <c r="O64" s="31"/>
-      <c r="P64" s="31"/>
-      <c r="Q64" s="31"/>
-      <c r="R64" s="31"/>
-      <c r="S64" s="31"/>
-      <c r="T64" s="31"/>
-      <c r="U64" s="31"/>
-      <c r="V64" s="31"/>
+      <c r="A64" s="31" t="s">
+        <v>318</v>
+      </c>
+      <c r="B64" s="32"/>
+      <c r="C64" s="32"/>
+      <c r="D64" s="32"/>
+      <c r="E64" s="32"/>
+      <c r="F64" s="32"/>
+      <c r="G64" s="32"/>
+      <c r="H64" s="32"/>
+      <c r="I64" s="32"/>
+      <c r="J64" s="32"/>
+      <c r="K64" s="32"/>
+      <c r="L64" s="32"/>
+      <c r="M64" s="32"/>
+      <c r="N64" s="32"/>
+      <c r="O64" s="32"/>
+      <c r="P64" s="32"/>
+      <c r="Q64" s="32"/>
+      <c r="R64" s="32"/>
+      <c r="S64" s="32"/>
+      <c r="T64" s="32"/>
+      <c r="U64" s="32"/>
+      <c r="V64" s="32"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="32" t="s">
-        <v>318</v>
-      </c>
-      <c r="B65" s="34">
+      <c r="A65" s="33" t="s">
+        <v>319</v>
+      </c>
+      <c r="B65" s="35">
         <v>8.22</v>
       </c>
-      <c r="C65" s="34">
+      <c r="C65" s="35">
         <v>6.01</v>
       </c>
-      <c r="D65" s="34">
+      <c r="D65" s="35">
         <v>6.95</v>
       </c>
-      <c r="E65" s="35"/>
-      <c r="F65" s="35"/>
-      <c r="G65" s="34">
+      <c r="E65" s="36"/>
+      <c r="F65" s="36"/>
+      <c r="G65" s="35">
         <v>25.19</v>
       </c>
-      <c r="H65" s="35"/>
-      <c r="I65" s="34">
+      <c r="H65" s="36"/>
+      <c r="I65" s="35">
         <v>4.7</v>
       </c>
-      <c r="J65" s="34">
+      <c r="J65" s="35">
         <v>51.46</v>
       </c>
-      <c r="K65" s="34">
+      <c r="K65" s="35">
         <v>3.57</v>
       </c>
-      <c r="L65" s="34">
+      <c r="L65" s="35">
         <v>1.0</v>
       </c>
-      <c r="M65" s="34">
+      <c r="M65" s="35">
         <v>4.71</v>
       </c>
-      <c r="N65" s="34">
+      <c r="N65" s="35">
         <v>3.08</v>
       </c>
-      <c r="O65" s="34">
+      <c r="O65" s="35">
         <v>4.73</v>
       </c>
-      <c r="P65" s="34">
+      <c r="P65" s="35">
         <v>3.15</v>
       </c>
-      <c r="Q65" s="34">
+      <c r="Q65" s="35">
         <v>4.22</v>
       </c>
-      <c r="R65" s="34">
+      <c r="R65" s="35">
         <v>1.43</v>
       </c>
-      <c r="S65" s="34">
+      <c r="S65" s="35">
         <v>5.14</v>
       </c>
-      <c r="T65" s="34">
+      <c r="T65" s="35">
         <v>7.28</v>
       </c>
-      <c r="U65" s="34">
+      <c r="U65" s="35">
         <v>5.57</v>
       </c>
-      <c r="V65" s="34">
+      <c r="V65" s="35">
         <v>4.72</v>
       </c>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="32" t="s">
-        <v>319</v>
-      </c>
-      <c r="B66" s="34">
+      <c r="A66" s="33" t="s">
+        <v>320</v>
+      </c>
+      <c r="B66" s="35">
         <v>59.5</v>
       </c>
-      <c r="C66" s="35"/>
-      <c r="D66" s="35"/>
-      <c r="E66" s="35"/>
-      <c r="F66" s="35"/>
-      <c r="G66" s="34">
+      <c r="C66" s="36"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="36"/>
+      <c r="G66" s="35">
         <v>20.12</v>
       </c>
-      <c r="H66" s="34">
+      <c r="H66" s="35">
         <v>11.15</v>
       </c>
-      <c r="I66" s="34">
+      <c r="I66" s="35">
         <v>5.18</v>
       </c>
-      <c r="J66" s="34">
+      <c r="J66" s="35">
         <v>4.93</v>
       </c>
-      <c r="K66" s="34">
+      <c r="K66" s="35">
         <v>2.99</v>
       </c>
-      <c r="L66" s="34">
+      <c r="L66" s="35">
         <v>2.88</v>
       </c>
-      <c r="M66" s="34">
+      <c r="M66" s="35">
         <v>3.89</v>
       </c>
-      <c r="N66" s="34">
+      <c r="N66" s="35">
         <v>3.26</v>
       </c>
-      <c r="O66" s="34">
+      <c r="O66" s="35">
         <v>3.69</v>
       </c>
-      <c r="P66" s="34">
+      <c r="P66" s="35">
         <v>4.16</v>
       </c>
-      <c r="Q66" s="34">
+      <c r="Q66" s="35">
         <v>4.63</v>
       </c>
-      <c r="R66" s="34">
+      <c r="R66" s="35">
         <v>4.73</v>
       </c>
-      <c r="S66" s="35"/>
-      <c r="T66" s="35"/>
-      <c r="U66" s="35"/>
-      <c r="V66" s="35"/>
+      <c r="S66" s="36"/>
+      <c r="T66" s="36"/>
+      <c r="U66" s="36"/>
+      <c r="V66" s="36"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="30" t="s">
-        <v>320</v>
-      </c>
-      <c r="B67" s="31"/>
-      <c r="C67" s="31"/>
-      <c r="D67" s="31"/>
-      <c r="E67" s="31"/>
-      <c r="F67" s="31"/>
-      <c r="G67" s="31"/>
-      <c r="H67" s="31"/>
-      <c r="I67" s="31"/>
-      <c r="J67" s="31"/>
-      <c r="K67" s="31"/>
-      <c r="L67" s="31"/>
-      <c r="M67" s="31"/>
-      <c r="N67" s="31"/>
-      <c r="O67" s="31"/>
-      <c r="P67" s="31"/>
-      <c r="Q67" s="31"/>
-      <c r="R67" s="31"/>
-      <c r="S67" s="31"/>
-      <c r="T67" s="31"/>
-      <c r="U67" s="31"/>
-      <c r="V67" s="31"/>
+      <c r="A67" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="B67" s="32"/>
+      <c r="C67" s="32"/>
+      <c r="D67" s="32"/>
+      <c r="E67" s="32"/>
+      <c r="F67" s="32"/>
+      <c r="G67" s="32"/>
+      <c r="H67" s="32"/>
+      <c r="I67" s="32"/>
+      <c r="J67" s="32"/>
+      <c r="K67" s="32"/>
+      <c r="L67" s="32"/>
+      <c r="M67" s="32"/>
+      <c r="N67" s="32"/>
+      <c r="O67" s="32"/>
+      <c r="P67" s="32"/>
+      <c r="Q67" s="32"/>
+      <c r="R67" s="32"/>
+      <c r="S67" s="32"/>
+      <c r="T67" s="32"/>
+      <c r="U67" s="32"/>
+      <c r="V67" s="32"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="32" t="s">
-        <v>321</v>
-      </c>
-      <c r="B68" s="34">
+      <c r="A68" s="33" t="s">
+        <v>322</v>
+      </c>
+      <c r="B68" s="35">
         <v>9.02</v>
       </c>
-      <c r="C68" s="34">
+      <c r="C68" s="35">
         <v>14.02</v>
       </c>
-      <c r="D68" s="34">
+      <c r="D68" s="35">
         <v>6.34</v>
       </c>
-      <c r="E68" s="34">
+      <c r="E68" s="35">
         <v>8.02</v>
       </c>
-      <c r="F68" s="35"/>
-      <c r="G68" s="34">
+      <c r="F68" s="36"/>
+      <c r="G68" s="35">
         <v>10.15</v>
       </c>
-      <c r="H68" s="35"/>
-      <c r="I68" s="34">
+      <c r="H68" s="36"/>
+      <c r="I68" s="35">
         <v>22.89</v>
       </c>
-      <c r="J68" s="35"/>
-      <c r="K68" s="34">
+      <c r="J68" s="36"/>
+      <c r="K68" s="35">
         <v>1.88</v>
       </c>
-      <c r="L68" s="34">
+      <c r="L68" s="35">
         <v>2.08</v>
       </c>
-      <c r="M68" s="34">
+      <c r="M68" s="35">
         <v>18.1</v>
       </c>
-      <c r="N68" s="34">
+      <c r="N68" s="35">
         <v>1.81</v>
       </c>
-      <c r="O68" s="34">
+      <c r="O68" s="35">
         <v>13.16</v>
       </c>
-      <c r="P68" s="34">
+      <c r="P68" s="35">
         <v>7.2</v>
       </c>
-      <c r="Q68" s="34">
+      <c r="Q68" s="35">
         <v>1.53</v>
       </c>
-      <c r="R68" s="34">
+      <c r="R68" s="35">
         <v>1.52</v>
       </c>
-      <c r="S68" s="34">
+      <c r="S68" s="35">
         <v>14.75</v>
       </c>
-      <c r="T68" s="34">
+      <c r="T68" s="35">
         <v>10.31</v>
       </c>
-      <c r="U68" s="34">
+      <c r="U68" s="35">
         <v>3.49</v>
       </c>
-      <c r="V68" s="34">
+      <c r="V68" s="35">
         <v>3.28</v>
       </c>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="32" t="s">
-        <v>322</v>
-      </c>
-      <c r="B69" s="34">
+      <c r="A69" s="33" t="s">
+        <v>323</v>
+      </c>
+      <c r="B69" s="35">
         <v>13.8</v>
       </c>
-      <c r="C69" s="34">
+      <c r="C69" s="35">
         <v>14.35</v>
       </c>
-      <c r="D69" s="34">
+      <c r="D69" s="35">
         <v>48.9</v>
       </c>
-      <c r="E69" s="33">
+      <c r="E69" s="34">
         <v>347.15</v>
       </c>
-      <c r="F69" s="35"/>
-      <c r="G69" s="34">
+      <c r="F69" s="36"/>
+      <c r="G69" s="35">
         <v>38.61</v>
       </c>
-      <c r="H69" s="34">
+      <c r="H69" s="35">
         <v>64.51</v>
       </c>
-      <c r="I69" s="34">
+      <c r="I69" s="35">
         <v>7.23</v>
       </c>
-      <c r="J69" s="34">
+      <c r="J69" s="35">
         <v>4.9</v>
       </c>
-      <c r="K69" s="34">
+      <c r="K69" s="35">
         <v>3.07</v>
       </c>
-      <c r="L69" s="34">
+      <c r="L69" s="35">
         <v>4.63</v>
       </c>
-      <c r="M69" s="34">
+      <c r="M69" s="35">
         <v>3.61</v>
       </c>
-      <c r="N69" s="34">
+      <c r="N69" s="35">
         <v>2.73</v>
       </c>
-      <c r="O69" s="34">
+      <c r="O69" s="35">
         <v>4.04</v>
       </c>
-      <c r="P69" s="34">
+      <c r="P69" s="35">
         <v>4.3</v>
       </c>
-      <c r="Q69" s="34">
+      <c r="Q69" s="35">
         <v>3.86</v>
       </c>
-      <c r="R69" s="34">
+      <c r="R69" s="35">
         <v>5.66</v>
       </c>
-      <c r="S69" s="35"/>
-      <c r="T69" s="35"/>
-      <c r="U69" s="35"/>
-      <c r="V69" s="35"/>
+      <c r="S69" s="36"/>
+      <c r="T69" s="36"/>
+      <c r="U69" s="36"/>
+      <c r="V69" s="36"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="30" t="s">
-        <v>323</v>
-      </c>
-      <c r="B70" s="31"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="31"/>
-      <c r="F70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="31"/>
-      <c r="I70" s="31"/>
-      <c r="J70" s="31"/>
-      <c r="K70" s="31"/>
-      <c r="L70" s="31"/>
-      <c r="M70" s="31"/>
-      <c r="N70" s="31"/>
-      <c r="O70" s="31"/>
-      <c r="P70" s="31"/>
-      <c r="Q70" s="31"/>
-      <c r="R70" s="31"/>
-      <c r="S70" s="31"/>
-      <c r="T70" s="31"/>
-      <c r="U70" s="31"/>
-      <c r="V70" s="31"/>
+      <c r="A70" s="31" t="s">
+        <v>324</v>
+      </c>
+      <c r="B70" s="32"/>
+      <c r="C70" s="32"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="32"/>
+      <c r="F70" s="32"/>
+      <c r="G70" s="32"/>
+      <c r="H70" s="32"/>
+      <c r="I70" s="32"/>
+      <c r="J70" s="32"/>
+      <c r="K70" s="32"/>
+      <c r="L70" s="32"/>
+      <c r="M70" s="32"/>
+      <c r="N70" s="32"/>
+      <c r="O70" s="32"/>
+      <c r="P70" s="32"/>
+      <c r="Q70" s="32"/>
+      <c r="R70" s="32"/>
+      <c r="S70" s="32"/>
+      <c r="T70" s="32"/>
+      <c r="U70" s="32"/>
+      <c r="V70" s="32"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="32" t="s">
-        <v>324</v>
-      </c>
-      <c r="B71" s="34">
+      <c r="A71" s="33" t="s">
+        <v>325</v>
+      </c>
+      <c r="B71" s="35">
         <v>11.27</v>
       </c>
-      <c r="C71" s="34">
+      <c r="C71" s="35">
         <v>50.01</v>
       </c>
-      <c r="D71" s="34">
+      <c r="D71" s="35">
         <v>7.21</v>
       </c>
-      <c r="E71" s="34">
+      <c r="E71" s="35">
         <v>8.14</v>
       </c>
-      <c r="F71" s="35"/>
-      <c r="G71" s="34">
+      <c r="F71" s="36"/>
+      <c r="G71" s="35">
         <v>12.16</v>
       </c>
-      <c r="H71" s="35"/>
-      <c r="I71" s="35"/>
-      <c r="J71" s="35"/>
-      <c r="K71" s="34">
+      <c r="H71" s="36"/>
+      <c r="I71" s="36"/>
+      <c r="J71" s="36"/>
+      <c r="K71" s="35">
         <v>2.41</v>
       </c>
-      <c r="L71" s="34">
+      <c r="L71" s="35">
         <v>4.53</v>
       </c>
-      <c r="M71" s="35"/>
-      <c r="N71" s="34">
+      <c r="M71" s="36"/>
+      <c r="N71" s="35">
         <v>2.48</v>
       </c>
-      <c r="O71" s="35"/>
-      <c r="P71" s="34">
+      <c r="O71" s="36"/>
+      <c r="P71" s="35">
         <v>10.28</v>
       </c>
-      <c r="Q71" s="34">
+      <c r="Q71" s="35">
         <v>1.54</v>
       </c>
-      <c r="R71" s="34">
+      <c r="R71" s="35">
         <v>1.55</v>
       </c>
-      <c r="S71" s="34">
+      <c r="S71" s="35">
         <v>15.3</v>
       </c>
-      <c r="T71" s="34">
+      <c r="T71" s="35">
         <v>10.76</v>
       </c>
-      <c r="U71" s="34">
+      <c r="U71" s="35">
         <v>3.59</v>
       </c>
-      <c r="V71" s="34">
+      <c r="V71" s="35">
         <v>3.49</v>
       </c>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="32" t="s">
-        <v>325</v>
-      </c>
-      <c r="B72" s="34">
+      <c r="A72" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="B72" s="35">
         <v>19.09</v>
       </c>
-      <c r="C72" s="34">
+      <c r="C72" s="35">
         <v>19.69</v>
       </c>
-      <c r="D72" s="33">
+      <c r="D72" s="34">
         <v>308.42</v>
       </c>
-      <c r="E72" s="35"/>
-      <c r="F72" s="35"/>
-      <c r="G72" s="35"/>
-      <c r="H72" s="35"/>
-      <c r="I72" s="34">
+      <c r="E72" s="36"/>
+      <c r="F72" s="36"/>
+      <c r="G72" s="36"/>
+      <c r="H72" s="36"/>
+      <c r="I72" s="35">
         <v>29.25</v>
       </c>
-      <c r="J72" s="34">
+      <c r="J72" s="35">
         <v>9.84</v>
       </c>
-      <c r="K72" s="34">
+      <c r="K72" s="35">
         <v>10.54</v>
       </c>
-      <c r="L72" s="35"/>
-      <c r="M72" s="34">
+      <c r="L72" s="36"/>
+      <c r="M72" s="35">
         <v>9.81</v>
       </c>
-      <c r="N72" s="34">
+      <c r="N72" s="35">
         <v>5.35</v>
       </c>
-      <c r="O72" s="34">
+      <c r="O72" s="35">
         <v>8.59</v>
       </c>
-      <c r="P72" s="34">
+      <c r="P72" s="35">
         <v>4.52</v>
       </c>
-      <c r="Q72" s="34">
+      <c r="Q72" s="35">
         <v>3.94</v>
       </c>
-      <c r="R72" s="34">
+      <c r="R72" s="35">
         <v>5.85</v>
       </c>
-      <c r="S72" s="35"/>
-      <c r="T72" s="35"/>
-      <c r="U72" s="35"/>
-      <c r="V72" s="35"/>
+      <c r="S72" s="36"/>
+      <c r="T72" s="36"/>
+      <c r="U72" s="36"/>
+      <c r="V72" s="36"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>
